--- a/data/ActivityContextGen_v09.xlsx
+++ b/data/ActivityContextGen_v09.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lucami Dropbox\Andrej Košir andrejgacc@gmail.com\000-Research\000-ElderlyRecSys\RecSysCode_v06\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gl8304\Documents\Projekti\Faks\Thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FDD37BC-0422-4ACD-9B3A-7E6036926915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31993129-8999-42BA-92E2-00B2C6EBE58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29325" yWindow="795" windowWidth="25875" windowHeight="16995" tabRatio="585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionLst" sheetId="1" r:id="rId1"/>
@@ -1896,12 +1896,12 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2128,34 +2128,34 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL1078"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="10.08203125" style="10" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="10" customWidth="1"/>
-    <col min="3" max="3" width="52.875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="52.83203125" style="10" customWidth="1"/>
     <col min="4" max="4" width="6.5" style="10" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="10" customWidth="1"/>
     <col min="6" max="6" width="5.75" style="10" customWidth="1"/>
-    <col min="7" max="7" width="7.875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="4.625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="5.25" style="10" customWidth="1"/>
+    <col min="7" max="7" width="7.83203125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="4.58203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="6.58203125" style="10" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="10" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="41.375" style="10" customWidth="1"/>
+    <col min="11" max="11" width="10.08203125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="41.33203125" style="10" customWidth="1"/>
     <col min="13" max="13" width="12.25" style="54" customWidth="1"/>
-    <col min="14" max="14" width="12.875" style="54" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="54" customWidth="1"/>
     <col min="15" max="15" width="12.25" style="54" customWidth="1"/>
     <col min="16" max="21" width="10.75" style="54" customWidth="1"/>
     <col min="22" max="22" width="12.25" style="10" customWidth="1"/>
     <col min="23" max="24" width="9" style="10" customWidth="1"/>
-    <col min="25" max="27" width="11.375" style="10" customWidth="1"/>
-    <col min="28" max="30" width="11.125" style="10" customWidth="1"/>
-    <col min="31" max="37" width="7.625" style="10" customWidth="1"/>
-    <col min="38" max="38" width="62.125" style="10" customWidth="1"/>
-    <col min="39" max="16384" width="12.625" style="10"/>
+    <col min="25" max="27" width="11.33203125" style="10" customWidth="1"/>
+    <col min="28" max="30" width="11.08203125" style="10" customWidth="1"/>
+    <col min="31" max="37" width="7.58203125" style="10" customWidth="1"/>
+    <col min="38" max="38" width="62.08203125" style="10" customWidth="1"/>
+    <col min="39" max="16384" width="12.58203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2257,7 +2257,7 @@
       <c r="AK1" s="7"/>
       <c r="AL1" s="7"/>
     </row>
-    <row r="2" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>11</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -2337,10 +2337,10 @@
       </c>
       <c r="T3" s="51"/>
       <c r="U3" s="51"/>
-      <c r="V3" s="64" t="s">
+      <c r="V3" s="62" t="s">
         <v>400</v>
       </c>
-      <c r="W3" s="64" t="s">
+      <c r="W3" s="62" t="s">
         <v>401</v>
       </c>
       <c r="X3" s="27"/>
@@ -2349,14 +2349,14 @@
       </c>
       <c r="Z3" s="29"/>
       <c r="AA3" s="29"/>
-      <c r="AB3" s="65" t="s">
+      <c r="AB3" s="63" t="s">
         <v>402</v>
       </c>
       <c r="AF3" s="15" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="T4" s="51"/>
       <c r="U4" s="51"/>
-      <c r="V4" s="64" t="s">
+      <c r="V4" s="62" t="s">
         <v>403</v>
       </c>
       <c r="W4" s="29" t="s">
@@ -2401,7 +2401,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
@@ -2444,7 +2444,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
@@ -2485,7 +2485,7 @@
       <c r="AA6" s="29"/>
       <c r="AF6" s="19"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="12"/>
@@ -2526,7 +2526,7 @@
       <c r="AA7" s="29"/>
       <c r="AF7" s="19"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12"/>
@@ -2567,7 +2567,7 @@
       <c r="AA8" s="29"/>
       <c r="AF8" s="19"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
@@ -2608,7 +2608,7 @@
       <c r="AA9" s="29"/>
       <c r="AF9" s="19"/>
     </row>
-    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
@@ -2652,7 +2652,7 @@
       <c r="Z10" s="27"/>
       <c r="AA10" s="27"/>
     </row>
-    <row r="11" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="Z11" s="29"/>
       <c r="AA11" s="27"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
@@ -2760,7 +2760,7 @@
       <c r="Z12" s="27"/>
       <c r="AA12" s="27"/>
     </row>
-    <row r="13" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -2800,7 +2800,7 @@
       <c r="Z13" s="27"/>
       <c r="AA13" s="27"/>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12"/>
@@ -2847,7 +2847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>11</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AA16" s="29"/>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AA17" s="29"/>
     </row>
-    <row r="18" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12"/>
@@ -3039,7 +3039,7 @@
       <c r="Z18" s="27"/>
       <c r="AA18" s="27"/>
     </row>
-    <row r="19" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
@@ -3158,7 +3158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12"/>
@@ -3215,7 +3215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
@@ -3265,7 +3265,7 @@
       <c r="Z22" s="27"/>
       <c r="AA22" s="27"/>
     </row>
-    <row r="23" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AA23" s="27"/>
     </row>
-    <row r="24" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>11</v>
       </c>
@@ -3365,7 +3365,7 @@
       <c r="Z24" s="27"/>
       <c r="AA24" s="27"/>
     </row>
-    <row r="25" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>11</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="AF26" s="19"/>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="T27" s="51"/>
       <c r="U27" s="51"/>
-      <c r="V27" s="64" t="s">
+      <c r="V27" s="62" t="s">
         <v>403</v>
       </c>
       <c r="W27" s="29" t="s">
@@ -3505,7 +3505,7 @@
       <c r="AA27" s="27"/>
       <c r="AF27" s="19"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12"/>
@@ -3546,7 +3546,7 @@
       <c r="AA28" s="27"/>
       <c r="AF28" s="19"/>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12"/>
@@ -3587,7 +3587,7 @@
       <c r="AA29" s="27"/>
       <c r="AF29" s="19"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
@@ -3628,7 +3628,7 @@
       <c r="AA30" s="27"/>
       <c r="AF30" s="19"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12"/>
@@ -3669,7 +3669,7 @@
       <c r="AA31" s="27"/>
       <c r="AF31" s="19"/>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12"/>
@@ -3710,7 +3710,7 @@
       <c r="AA32" s="27"/>
       <c r="AF32" s="19"/>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12"/>
@@ -3755,7 +3755,7 @@
       <c r="AA33" s="27"/>
       <c r="AF33" s="19"/>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12"/>
@@ -3806,7 +3806,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12"/>
@@ -3857,7 +3857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:38" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
         <v>51</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12"/>
@@ -3964,7 +3964,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" s="21"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12"/>
@@ -4015,7 +4015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
         <v>51</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="23"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12"/>
@@ -4122,7 +4122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="58" x14ac:dyDescent="0.35">
       <c r="A41" s="23"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -4173,7 +4173,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:38" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="23" t="s">
         <v>57</v>
       </c>
@@ -4222,17 +4222,17 @@
       <c r="Y42" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="AF42" s="62" t="s">
+      <c r="AF42" s="64" t="s">
         <v>163</v>
       </c>
-      <c r="AG42" s="63"/>
-      <c r="AH42" s="63"/>
-      <c r="AI42" s="63"/>
-      <c r="AJ42" s="63"/>
-      <c r="AK42" s="63"/>
-      <c r="AL42" s="63"/>
-    </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AG42" s="65"/>
+      <c r="AH42" s="65"/>
+      <c r="AI42" s="65"/>
+      <c r="AJ42" s="65"/>
+      <c r="AK42" s="65"/>
+      <c r="AL42" s="65"/>
+    </row>
+    <row r="43" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="23"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -4274,7 +4274,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="23" t="s">
         <v>57</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="23"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
@@ -4387,7 +4387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:38" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="58" x14ac:dyDescent="0.35">
       <c r="A46" s="23"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12"/>
@@ -4438,7 +4438,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="23"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12"/>
@@ -4489,7 +4489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:38" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="23"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12"/>
@@ -4540,7 +4540,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="23"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12"/>
@@ -4588,7 +4588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="23"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12"/>
@@ -4633,7 +4633,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="23"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12"/>
@@ -4681,7 +4681,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="23"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12"/>
@@ -4729,7 +4729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="23" t="s">
         <v>57</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="23"/>
       <c r="B54" s="11"/>
       <c r="C54" s="12"/>
@@ -4824,7 +4824,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="23" t="s">
         <v>57</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="23"/>
       <c r="B56" s="11"/>
       <c r="C56" s="12"/>
@@ -4937,7 +4937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" ht="58" x14ac:dyDescent="0.35">
       <c r="A57" s="23"/>
       <c r="B57" s="11"/>
       <c r="C57" s="12"/>
@@ -4988,7 +4988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="23"/>
       <c r="B58" s="11"/>
       <c r="C58" s="12"/>
@@ -5039,7 +5039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="23"/>
       <c r="B59" s="11"/>
       <c r="C59" s="12"/>
@@ -5090,7 +5090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="23"/>
       <c r="B60" s="11"/>
       <c r="C60" s="12"/>
@@ -5138,7 +5138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="23"/>
       <c r="B61" s="11"/>
       <c r="C61" s="12"/>
@@ -5183,7 +5183,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="23"/>
       <c r="B62" s="11"/>
       <c r="C62" s="12"/>
@@ -5231,7 +5231,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="23"/>
       <c r="B63" s="11"/>
       <c r="C63" s="12"/>
@@ -5279,7 +5279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
         <v>57</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="23"/>
       <c r="B65" s="11"/>
       <c r="C65" s="12"/>
@@ -5392,7 +5392,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="23"/>
       <c r="B66" s="11"/>
       <c r="C66" s="12"/>
@@ -5443,7 +5443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="23"/>
       <c r="B67" s="11"/>
       <c r="C67" s="12"/>
@@ -5494,7 +5494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="23" t="s">
         <v>57</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="23"/>
       <c r="B69" s="11"/>
       <c r="C69" s="12"/>
@@ -5607,7 +5607,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="23"/>
       <c r="B70" s="11"/>
       <c r="C70" s="12"/>
@@ -5658,7 +5658,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="23" t="s">
         <v>57</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="21"/>
       <c r="B72" s="11"/>
       <c r="C72" s="12"/>
@@ -5771,7 +5771,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="21"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
@@ -5819,7 +5819,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="21"/>
       <c r="B74" s="11"/>
       <c r="C74" s="12"/>
@@ -5867,7 +5867,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="21"/>
       <c r="B75" s="11"/>
       <c r="C75" s="12"/>
@@ -5906,7 +5906,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="21" t="s">
         <v>77</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="21"/>
       <c r="B77" s="11"/>
       <c r="C77" s="12"/>
@@ -5989,7 +5989,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="21"/>
       <c r="B78" s="11"/>
       <c r="C78" s="12"/>
@@ -6031,7 +6031,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="21" t="s">
         <v>77</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="21"/>
       <c r="B80" s="11"/>
       <c r="C80" s="12"/>
@@ -6135,7 +6135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="21"/>
       <c r="B81" s="11"/>
       <c r="C81" s="12"/>
@@ -6183,7 +6183,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="21"/>
       <c r="B82" s="11"/>
       <c r="C82" s="12"/>
@@ -6222,7 +6222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="21"/>
       <c r="B83" s="11"/>
       <c r="C83" s="12"/>
@@ -6258,7 +6258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="21"/>
       <c r="B84" s="11"/>
       <c r="C84" s="12"/>
@@ -6297,7 +6297,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="21"/>
       <c r="B85" s="11"/>
       <c r="C85" s="12"/>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="21"/>
       <c r="B86" s="11"/>
       <c r="C86" s="12"/>
@@ -6375,7 +6375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="21"/>
       <c r="B87" s="11"/>
       <c r="C87" s="12"/>
@@ -6411,7 +6411,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="21"/>
       <c r="B88" s="11"/>
       <c r="C88" s="12"/>
@@ -6450,7 +6450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="21"/>
       <c r="B89" s="11"/>
       <c r="C89" s="12"/>
@@ -6489,7 +6489,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="21" t="s">
         <v>77</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="91" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="21"/>
       <c r="B91" s="11"/>
       <c r="C91" s="12"/>
@@ -6587,7 +6587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="21"/>
       <c r="B92" s="11"/>
       <c r="C92" s="12"/>
@@ -6632,7 +6632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="21" t="s">
         <v>77</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="21"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12"/>
@@ -6709,7 +6709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="21"/>
       <c r="B95" s="11"/>
       <c r="C95" s="12"/>
@@ -6760,7 +6760,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="96" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="21" t="s">
         <v>77</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="21"/>
       <c r="B97" s="11"/>
       <c r="C97" s="12"/>
@@ -6852,7 +6852,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="21"/>
       <c r="B98" s="11"/>
       <c r="C98" s="12"/>
@@ -6903,7 +6903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="21" t="s">
         <v>109</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="21"/>
       <c r="B100" s="11"/>
       <c r="C100" s="12"/>
@@ -6983,7 +6983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="21"/>
       <c r="B101" s="11"/>
       <c r="C101" s="12"/>
@@ -7019,7 +7019,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="21" t="s">
         <v>109</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="21"/>
       <c r="B103" s="11"/>
       <c r="C103" s="25"/>
@@ -7096,7 +7096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="21"/>
       <c r="B104" s="11"/>
       <c r="C104" s="25"/>
@@ -7132,7 +7132,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="21" t="s">
         <v>109</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="33"/>
       <c r="B106" s="37"/>
       <c r="C106" s="35"/>
@@ -7212,7 +7212,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="32"/>
       <c r="B107" s="37"/>
       <c r="C107" s="38"/>
@@ -7248,3887 +7248,3887 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C108" s="14"/>
       <c r="L108" s="14"/>
     </row>
-    <row r="109" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C109" s="14"/>
       <c r="L109" s="14"/>
     </row>
-    <row r="110" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C110" s="14"/>
       <c r="L110" s="14"/>
     </row>
-    <row r="111" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C111" s="14"/>
       <c r="L111" s="14"/>
     </row>
-    <row r="112" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C112" s="14"/>
       <c r="L112" s="14"/>
     </row>
-    <row r="113" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C113" s="14"/>
       <c r="L113" s="14"/>
     </row>
-    <row r="114" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C114" s="14"/>
       <c r="L114" s="14"/>
     </row>
-    <row r="115" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="14"/>
       <c r="L115" s="14"/>
     </row>
-    <row r="116" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C116" s="14"/>
       <c r="L116" s="14"/>
     </row>
-    <row r="117" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C117" s="14"/>
       <c r="L117" s="14"/>
     </row>
-    <row r="118" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C118" s="14"/>
       <c r="L118" s="14"/>
     </row>
-    <row r="119" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C119" s="14"/>
       <c r="L119" s="14"/>
     </row>
-    <row r="120" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C120" s="14"/>
       <c r="L120" s="14"/>
     </row>
-    <row r="121" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C121" s="14"/>
       <c r="L121" s="14"/>
     </row>
-    <row r="122" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C122" s="14"/>
       <c r="L122" s="14"/>
     </row>
-    <row r="123" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C123" s="14"/>
       <c r="L123" s="14"/>
     </row>
-    <row r="124" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C124" s="14"/>
       <c r="L124" s="14"/>
     </row>
-    <row r="125" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C125" s="14"/>
       <c r="L125" s="14"/>
     </row>
-    <row r="126" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C126" s="14"/>
       <c r="L126" s="14"/>
     </row>
-    <row r="127" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C127" s="14"/>
       <c r="L127" s="14"/>
     </row>
-    <row r="128" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C128" s="14"/>
       <c r="L128" s="14"/>
     </row>
-    <row r="129" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C129" s="14"/>
       <c r="L129" s="14"/>
     </row>
-    <row r="130" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C130" s="14"/>
       <c r="L130" s="14"/>
     </row>
-    <row r="131" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C131" s="14"/>
       <c r="L131" s="14"/>
     </row>
-    <row r="132" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C132" s="14"/>
       <c r="L132" s="14"/>
     </row>
-    <row r="133" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C133" s="14"/>
       <c r="L133" s="14"/>
     </row>
-    <row r="134" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C134" s="14"/>
       <c r="L134" s="14"/>
     </row>
-    <row r="135" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C135" s="14"/>
       <c r="L135" s="14"/>
     </row>
-    <row r="136" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C136" s="14"/>
       <c r="L136" s="14"/>
     </row>
-    <row r="137" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C137" s="14"/>
       <c r="L137" s="14"/>
     </row>
-    <row r="138" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C138" s="14"/>
       <c r="L138" s="14"/>
     </row>
-    <row r="139" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C139" s="14"/>
       <c r="L139" s="14"/>
     </row>
-    <row r="140" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C140" s="14"/>
       <c r="L140" s="14"/>
     </row>
-    <row r="141" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C141" s="14"/>
       <c r="L141" s="14"/>
     </row>
-    <row r="142" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C142" s="14"/>
       <c r="L142" s="14"/>
     </row>
-    <row r="143" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C143" s="14"/>
       <c r="L143" s="14"/>
     </row>
-    <row r="144" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C144" s="14"/>
       <c r="L144" s="14"/>
     </row>
-    <row r="145" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C145" s="14"/>
       <c r="L145" s="14"/>
     </row>
-    <row r="146" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C146" s="14"/>
       <c r="L146" s="14"/>
     </row>
-    <row r="147" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C147" s="14"/>
       <c r="L147" s="14"/>
     </row>
-    <row r="148" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C148" s="14"/>
       <c r="L148" s="14"/>
     </row>
-    <row r="149" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C149" s="14"/>
       <c r="L149" s="14"/>
     </row>
-    <row r="150" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C150" s="14"/>
       <c r="L150" s="14"/>
     </row>
-    <row r="151" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C151" s="14"/>
       <c r="L151" s="14"/>
     </row>
-    <row r="152" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C152" s="14"/>
       <c r="L152" s="14"/>
     </row>
-    <row r="153" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C153" s="14"/>
       <c r="L153" s="14"/>
     </row>
-    <row r="154" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C154" s="14"/>
       <c r="L154" s="14"/>
     </row>
-    <row r="155" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C155" s="14"/>
       <c r="L155" s="14"/>
     </row>
-    <row r="156" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C156" s="14"/>
       <c r="L156" s="14"/>
     </row>
-    <row r="157" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C157" s="14"/>
       <c r="L157" s="14"/>
     </row>
-    <row r="158" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C158" s="14"/>
       <c r="L158" s="14"/>
     </row>
-    <row r="159" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C159" s="14"/>
       <c r="L159" s="14"/>
     </row>
-    <row r="160" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C160" s="14"/>
       <c r="L160" s="14"/>
     </row>
-    <row r="161" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C161" s="14"/>
       <c r="L161" s="14"/>
     </row>
-    <row r="162" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C162" s="14"/>
       <c r="L162" s="14"/>
     </row>
-    <row r="163" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C163" s="14"/>
       <c r="L163" s="14"/>
     </row>
-    <row r="164" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C164" s="14"/>
       <c r="L164" s="14"/>
     </row>
-    <row r="165" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C165" s="14"/>
       <c r="L165" s="14"/>
     </row>
-    <row r="166" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C166" s="14"/>
       <c r="L166" s="14"/>
     </row>
-    <row r="167" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C167" s="14"/>
       <c r="L167" s="14"/>
     </row>
-    <row r="168" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C168" s="14"/>
       <c r="L168" s="14"/>
     </row>
-    <row r="169" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C169" s="14"/>
       <c r="L169" s="14"/>
     </row>
-    <row r="170" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C170" s="14"/>
       <c r="L170" s="14"/>
     </row>
-    <row r="171" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C171" s="14"/>
       <c r="L171" s="14"/>
     </row>
-    <row r="172" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C172" s="14"/>
       <c r="L172" s="14"/>
     </row>
-    <row r="173" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C173" s="14"/>
       <c r="L173" s="14"/>
     </row>
-    <row r="174" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C174" s="14"/>
       <c r="L174" s="14"/>
     </row>
-    <row r="175" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C175" s="14"/>
       <c r="L175" s="14"/>
     </row>
-    <row r="176" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C176" s="14"/>
       <c r="L176" s="14"/>
     </row>
-    <row r="177" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C177" s="14"/>
       <c r="L177" s="14"/>
     </row>
-    <row r="178" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C178" s="14"/>
       <c r="L178" s="14"/>
     </row>
-    <row r="179" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C179" s="14"/>
       <c r="L179" s="14"/>
     </row>
-    <row r="180" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C180" s="14"/>
       <c r="L180" s="14"/>
     </row>
-    <row r="181" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C181" s="14"/>
       <c r="L181" s="14"/>
     </row>
-    <row r="182" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C182" s="14"/>
       <c r="L182" s="14"/>
     </row>
-    <row r="183" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C183" s="14"/>
       <c r="L183" s="14"/>
     </row>
-    <row r="184" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C184" s="14"/>
       <c r="L184" s="14"/>
     </row>
-    <row r="185" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C185" s="14"/>
       <c r="L185" s="14"/>
     </row>
-    <row r="186" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C186" s="14"/>
       <c r="L186" s="14"/>
     </row>
-    <row r="187" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C187" s="14"/>
       <c r="L187" s="14"/>
     </row>
-    <row r="188" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C188" s="14"/>
       <c r="L188" s="14"/>
     </row>
-    <row r="189" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C189" s="14"/>
       <c r="L189" s="14"/>
     </row>
-    <row r="190" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C190" s="14"/>
       <c r="L190" s="14"/>
     </row>
-    <row r="191" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C191" s="14"/>
       <c r="L191" s="14"/>
     </row>
-    <row r="192" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C192" s="14"/>
       <c r="L192" s="14"/>
     </row>
-    <row r="193" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C193" s="14"/>
       <c r="L193" s="14"/>
     </row>
-    <row r="194" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C194" s="14"/>
       <c r="L194" s="14"/>
     </row>
-    <row r="195" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C195" s="14"/>
       <c r="L195" s="14"/>
     </row>
-    <row r="196" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C196" s="14"/>
       <c r="L196" s="14"/>
     </row>
-    <row r="197" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C197" s="14"/>
       <c r="L197" s="14"/>
     </row>
-    <row r="198" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C198" s="14"/>
       <c r="L198" s="14"/>
     </row>
-    <row r="199" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C199" s="14"/>
       <c r="L199" s="14"/>
     </row>
-    <row r="200" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C200" s="14"/>
       <c r="L200" s="14"/>
     </row>
-    <row r="201" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C201" s="14"/>
       <c r="L201" s="14"/>
     </row>
-    <row r="202" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C202" s="14"/>
       <c r="L202" s="14"/>
     </row>
-    <row r="203" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C203" s="14"/>
       <c r="L203" s="14"/>
     </row>
-    <row r="204" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C204" s="14"/>
       <c r="L204" s="14"/>
     </row>
-    <row r="205" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C205" s="14"/>
       <c r="L205" s="14"/>
     </row>
-    <row r="206" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C206" s="14"/>
       <c r="L206" s="14"/>
     </row>
-    <row r="207" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C207" s="14"/>
       <c r="L207" s="14"/>
     </row>
-    <row r="208" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C208" s="14"/>
       <c r="L208" s="14"/>
     </row>
-    <row r="209" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C209" s="14"/>
       <c r="L209" s="14"/>
     </row>
-    <row r="210" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C210" s="14"/>
       <c r="L210" s="14"/>
     </row>
-    <row r="211" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C211" s="14"/>
       <c r="L211" s="14"/>
     </row>
-    <row r="212" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C212" s="14"/>
       <c r="L212" s="14"/>
     </row>
-    <row r="213" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C213" s="14"/>
       <c r="L213" s="14"/>
     </row>
-    <row r="214" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C214" s="14"/>
       <c r="L214" s="14"/>
     </row>
-    <row r="215" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C215" s="14"/>
       <c r="L215" s="14"/>
     </row>
-    <row r="216" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C216" s="14"/>
       <c r="L216" s="14"/>
     </row>
-    <row r="217" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C217" s="14"/>
       <c r="L217" s="14"/>
     </row>
-    <row r="218" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C218" s="14"/>
       <c r="L218" s="14"/>
     </row>
-    <row r="219" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C219" s="14"/>
       <c r="L219" s="14"/>
     </row>
-    <row r="220" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C220" s="14"/>
       <c r="L220" s="14"/>
     </row>
-    <row r="221" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C221" s="14"/>
       <c r="L221" s="14"/>
     </row>
-    <row r="222" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C222" s="14"/>
       <c r="L222" s="14"/>
     </row>
-    <row r="223" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C223" s="14"/>
       <c r="L223" s="14"/>
     </row>
-    <row r="224" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C224" s="14"/>
       <c r="L224" s="14"/>
     </row>
-    <row r="225" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C225" s="14"/>
       <c r="L225" s="14"/>
     </row>
-    <row r="226" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C226" s="14"/>
       <c r="L226" s="14"/>
     </row>
-    <row r="227" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C227" s="14"/>
       <c r="L227" s="14"/>
     </row>
-    <row r="228" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C228" s="14"/>
       <c r="L228" s="14"/>
     </row>
-    <row r="229" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C229" s="14"/>
       <c r="L229" s="14"/>
     </row>
-    <row r="230" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C230" s="14"/>
       <c r="L230" s="14"/>
     </row>
-    <row r="231" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C231" s="14"/>
       <c r="L231" s="14"/>
     </row>
-    <row r="232" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C232" s="14"/>
       <c r="L232" s="14"/>
     </row>
-    <row r="233" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C233" s="14"/>
       <c r="L233" s="14"/>
     </row>
-    <row r="234" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C234" s="14"/>
       <c r="L234" s="14"/>
     </row>
-    <row r="235" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C235" s="14"/>
       <c r="L235" s="14"/>
     </row>
-    <row r="236" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C236" s="14"/>
       <c r="L236" s="14"/>
     </row>
-    <row r="237" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C237" s="14"/>
       <c r="L237" s="14"/>
     </row>
-    <row r="238" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C238" s="14"/>
       <c r="L238" s="14"/>
     </row>
-    <row r="239" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C239" s="14"/>
       <c r="L239" s="14"/>
     </row>
-    <row r="240" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C240" s="14"/>
       <c r="L240" s="14"/>
     </row>
-    <row r="241" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C241" s="14"/>
       <c r="L241" s="14"/>
     </row>
-    <row r="242" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C242" s="14"/>
       <c r="L242" s="14"/>
     </row>
-    <row r="243" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C243" s="14"/>
       <c r="L243" s="14"/>
     </row>
-    <row r="244" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C244" s="14"/>
       <c r="L244" s="14"/>
     </row>
-    <row r="245" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C245" s="14"/>
       <c r="L245" s="14"/>
     </row>
-    <row r="246" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C246" s="14"/>
       <c r="L246" s="14"/>
     </row>
-    <row r="247" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C247" s="14"/>
       <c r="L247" s="14"/>
     </row>
-    <row r="248" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C248" s="14"/>
       <c r="L248" s="14"/>
     </row>
-    <row r="249" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C249" s="14"/>
       <c r="L249" s="14"/>
     </row>
-    <row r="250" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C250" s="14"/>
       <c r="L250" s="14"/>
     </row>
-    <row r="251" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C251" s="14"/>
       <c r="L251" s="14"/>
     </row>
-    <row r="252" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C252" s="14"/>
       <c r="L252" s="14"/>
     </row>
-    <row r="253" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C253" s="14"/>
       <c r="L253" s="14"/>
     </row>
-    <row r="254" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C254" s="14"/>
       <c r="L254" s="14"/>
     </row>
-    <row r="255" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C255" s="14"/>
       <c r="L255" s="14"/>
     </row>
-    <row r="256" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C256" s="14"/>
       <c r="L256" s="14"/>
     </row>
-    <row r="257" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C257" s="14"/>
       <c r="L257" s="14"/>
     </row>
-    <row r="258" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C258" s="14"/>
       <c r="L258" s="14"/>
     </row>
-    <row r="259" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C259" s="14"/>
       <c r="L259" s="14"/>
     </row>
-    <row r="260" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C260" s="14"/>
       <c r="L260" s="14"/>
     </row>
-    <row r="261" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C261" s="14"/>
       <c r="L261" s="14"/>
     </row>
-    <row r="262" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C262" s="14"/>
       <c r="L262" s="14"/>
     </row>
-    <row r="263" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C263" s="14"/>
       <c r="L263" s="14"/>
     </row>
-    <row r="264" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C264" s="14"/>
       <c r="L264" s="14"/>
     </row>
-    <row r="265" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C265" s="14"/>
       <c r="L265" s="14"/>
     </row>
-    <row r="266" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C266" s="14"/>
       <c r="L266" s="14"/>
     </row>
-    <row r="267" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C267" s="14"/>
       <c r="L267" s="14"/>
     </row>
-    <row r="268" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C268" s="14"/>
       <c r="L268" s="14"/>
     </row>
-    <row r="269" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C269" s="14"/>
       <c r="L269" s="14"/>
     </row>
-    <row r="270" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C270" s="14"/>
       <c r="L270" s="14"/>
     </row>
-    <row r="271" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C271" s="14"/>
       <c r="L271" s="14"/>
     </row>
-    <row r="272" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C272" s="14"/>
       <c r="L272" s="14"/>
     </row>
-    <row r="273" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C273" s="14"/>
       <c r="L273" s="14"/>
     </row>
-    <row r="274" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C274" s="14"/>
       <c r="L274" s="14"/>
     </row>
-    <row r="275" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C275" s="14"/>
       <c r="L275" s="14"/>
     </row>
-    <row r="276" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C276" s="14"/>
       <c r="L276" s="14"/>
     </row>
-    <row r="277" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C277" s="14"/>
       <c r="L277" s="14"/>
     </row>
-    <row r="278" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C278" s="14"/>
       <c r="L278" s="14"/>
     </row>
-    <row r="279" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C279" s="14"/>
       <c r="L279" s="14"/>
     </row>
-    <row r="280" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C280" s="14"/>
       <c r="L280" s="14"/>
     </row>
-    <row r="281" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C281" s="14"/>
       <c r="L281" s="14"/>
     </row>
-    <row r="282" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C282" s="14"/>
       <c r="L282" s="14"/>
     </row>
-    <row r="283" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C283" s="14"/>
       <c r="L283" s="14"/>
     </row>
-    <row r="284" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C284" s="14"/>
       <c r="L284" s="14"/>
     </row>
-    <row r="285" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C285" s="14"/>
       <c r="L285" s="14"/>
     </row>
-    <row r="286" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C286" s="14"/>
       <c r="L286" s="14"/>
     </row>
-    <row r="287" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C287" s="14"/>
       <c r="L287" s="14"/>
     </row>
-    <row r="288" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C288" s="14"/>
       <c r="L288" s="14"/>
     </row>
-    <row r="289" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C289" s="14"/>
       <c r="L289" s="14"/>
     </row>
-    <row r="290" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C290" s="14"/>
       <c r="L290" s="14"/>
     </row>
-    <row r="291" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C291" s="14"/>
       <c r="L291" s="14"/>
     </row>
-    <row r="292" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C292" s="14"/>
       <c r="L292" s="14"/>
     </row>
-    <row r="293" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C293" s="14"/>
       <c r="L293" s="14"/>
     </row>
-    <row r="294" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C294" s="14"/>
       <c r="L294" s="14"/>
     </row>
-    <row r="295" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C295" s="14"/>
       <c r="L295" s="14"/>
     </row>
-    <row r="296" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C296" s="14"/>
       <c r="L296" s="14"/>
     </row>
-    <row r="297" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C297" s="14"/>
       <c r="L297" s="14"/>
     </row>
-    <row r="298" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C298" s="14"/>
       <c r="L298" s="14"/>
     </row>
-    <row r="299" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C299" s="14"/>
       <c r="L299" s="14"/>
     </row>
-    <row r="300" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C300" s="14"/>
       <c r="L300" s="14"/>
     </row>
-    <row r="301" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C301" s="14"/>
       <c r="L301" s="14"/>
     </row>
-    <row r="302" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C302" s="14"/>
       <c r="L302" s="14"/>
     </row>
-    <row r="303" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C303" s="14"/>
       <c r="L303" s="14"/>
     </row>
-    <row r="304" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C304" s="14"/>
       <c r="L304" s="14"/>
     </row>
-    <row r="305" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C305" s="14"/>
       <c r="L305" s="14"/>
     </row>
-    <row r="306" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C306" s="14"/>
       <c r="L306" s="14"/>
     </row>
-    <row r="307" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C307" s="14"/>
       <c r="L307" s="14"/>
     </row>
-    <row r="308" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C308" s="14"/>
       <c r="L308" s="14"/>
     </row>
-    <row r="309" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C309" s="14"/>
       <c r="L309" s="14"/>
     </row>
-    <row r="310" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C310" s="14"/>
       <c r="L310" s="14"/>
     </row>
-    <row r="311" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C311" s="14"/>
       <c r="L311" s="14"/>
     </row>
-    <row r="312" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C312" s="14"/>
       <c r="L312" s="14"/>
     </row>
-    <row r="313" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C313" s="14"/>
       <c r="L313" s="14"/>
     </row>
-    <row r="314" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C314" s="14"/>
       <c r="L314" s="14"/>
     </row>
-    <row r="315" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C315" s="14"/>
       <c r="L315" s="14"/>
     </row>
-    <row r="316" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C316" s="14"/>
       <c r="L316" s="14"/>
     </row>
-    <row r="317" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C317" s="14"/>
       <c r="L317" s="14"/>
     </row>
-    <row r="318" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C318" s="14"/>
       <c r="L318" s="14"/>
     </row>
-    <row r="319" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C319" s="14"/>
       <c r="L319" s="14"/>
     </row>
-    <row r="320" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C320" s="14"/>
       <c r="L320" s="14"/>
     </row>
-    <row r="321" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C321" s="14"/>
       <c r="L321" s="14"/>
     </row>
-    <row r="322" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C322" s="14"/>
       <c r="L322" s="14"/>
     </row>
-    <row r="323" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C323" s="14"/>
       <c r="L323" s="14"/>
     </row>
-    <row r="324" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C324" s="14"/>
       <c r="L324" s="14"/>
     </row>
-    <row r="325" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C325" s="14"/>
       <c r="L325" s="14"/>
     </row>
-    <row r="326" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C326" s="14"/>
       <c r="L326" s="14"/>
     </row>
-    <row r="327" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C327" s="14"/>
       <c r="L327" s="14"/>
     </row>
-    <row r="328" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C328" s="14"/>
       <c r="L328" s="14"/>
     </row>
-    <row r="329" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C329" s="14"/>
       <c r="L329" s="14"/>
     </row>
-    <row r="330" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C330" s="14"/>
       <c r="L330" s="14"/>
     </row>
-    <row r="331" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C331" s="14"/>
       <c r="L331" s="14"/>
     </row>
-    <row r="332" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C332" s="14"/>
       <c r="L332" s="14"/>
     </row>
-    <row r="333" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C333" s="14"/>
       <c r="L333" s="14"/>
     </row>
-    <row r="334" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C334" s="14"/>
       <c r="L334" s="14"/>
     </row>
-    <row r="335" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C335" s="14"/>
       <c r="L335" s="14"/>
     </row>
-    <row r="336" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C336" s="14"/>
       <c r="L336" s="14"/>
     </row>
-    <row r="337" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C337" s="14"/>
       <c r="L337" s="14"/>
     </row>
-    <row r="338" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C338" s="14"/>
       <c r="L338" s="14"/>
     </row>
-    <row r="339" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C339" s="14"/>
       <c r="L339" s="14"/>
     </row>
-    <row r="340" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C340" s="14"/>
       <c r="L340" s="14"/>
     </row>
-    <row r="341" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C341" s="14"/>
       <c r="L341" s="14"/>
     </row>
-    <row r="342" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C342" s="14"/>
       <c r="L342" s="14"/>
     </row>
-    <row r="343" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C343" s="14"/>
       <c r="L343" s="14"/>
     </row>
-    <row r="344" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C344" s="14"/>
       <c r="L344" s="14"/>
     </row>
-    <row r="345" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C345" s="14"/>
       <c r="L345" s="14"/>
     </row>
-    <row r="346" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C346" s="14"/>
       <c r="L346" s="14"/>
     </row>
-    <row r="347" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C347" s="14"/>
       <c r="L347" s="14"/>
     </row>
-    <row r="348" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C348" s="14"/>
       <c r="L348" s="14"/>
     </row>
-    <row r="349" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C349" s="14"/>
       <c r="L349" s="14"/>
     </row>
-    <row r="350" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C350" s="14"/>
       <c r="L350" s="14"/>
     </row>
-    <row r="351" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C351" s="14"/>
       <c r="L351" s="14"/>
     </row>
-    <row r="352" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C352" s="14"/>
       <c r="L352" s="14"/>
     </row>
-    <row r="353" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C353" s="14"/>
       <c r="L353" s="14"/>
     </row>
-    <row r="354" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C354" s="14"/>
       <c r="L354" s="14"/>
     </row>
-    <row r="355" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C355" s="14"/>
       <c r="L355" s="14"/>
     </row>
-    <row r="356" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C356" s="14"/>
       <c r="L356" s="14"/>
     </row>
-    <row r="357" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C357" s="14"/>
       <c r="L357" s="14"/>
     </row>
-    <row r="358" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C358" s="14"/>
       <c r="L358" s="14"/>
     </row>
-    <row r="359" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C359" s="14"/>
       <c r="L359" s="14"/>
     </row>
-    <row r="360" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C360" s="14"/>
       <c r="L360" s="14"/>
     </row>
-    <row r="361" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C361" s="14"/>
       <c r="L361" s="14"/>
     </row>
-    <row r="362" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C362" s="14"/>
       <c r="L362" s="14"/>
     </row>
-    <row r="363" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C363" s="14"/>
       <c r="L363" s="14"/>
     </row>
-    <row r="364" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C364" s="14"/>
       <c r="L364" s="14"/>
     </row>
-    <row r="365" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C365" s="14"/>
       <c r="L365" s="14"/>
     </row>
-    <row r="366" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C366" s="14"/>
       <c r="L366" s="14"/>
     </row>
-    <row r="367" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C367" s="14"/>
       <c r="L367" s="14"/>
     </row>
-    <row r="368" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C368" s="14"/>
       <c r="L368" s="14"/>
     </row>
-    <row r="369" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C369" s="14"/>
       <c r="L369" s="14"/>
     </row>
-    <row r="370" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C370" s="14"/>
       <c r="L370" s="14"/>
     </row>
-    <row r="371" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C371" s="14"/>
       <c r="L371" s="14"/>
     </row>
-    <row r="372" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C372" s="14"/>
       <c r="L372" s="14"/>
     </row>
-    <row r="373" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C373" s="14"/>
       <c r="L373" s="14"/>
     </row>
-    <row r="374" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C374" s="14"/>
       <c r="L374" s="14"/>
     </row>
-    <row r="375" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C375" s="14"/>
       <c r="L375" s="14"/>
     </row>
-    <row r="376" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C376" s="14"/>
       <c r="L376" s="14"/>
     </row>
-    <row r="377" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C377" s="14"/>
       <c r="L377" s="14"/>
     </row>
-    <row r="378" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C378" s="14"/>
       <c r="L378" s="14"/>
     </row>
-    <row r="379" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C379" s="14"/>
       <c r="L379" s="14"/>
     </row>
-    <row r="380" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C380" s="14"/>
       <c r="L380" s="14"/>
     </row>
-    <row r="381" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C381" s="14"/>
       <c r="L381" s="14"/>
     </row>
-    <row r="382" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C382" s="14"/>
       <c r="L382" s="14"/>
     </row>
-    <row r="383" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C383" s="14"/>
       <c r="L383" s="14"/>
     </row>
-    <row r="384" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C384" s="14"/>
       <c r="L384" s="14"/>
     </row>
-    <row r="385" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C385" s="14"/>
       <c r="L385" s="14"/>
     </row>
-    <row r="386" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C386" s="14"/>
       <c r="L386" s="14"/>
     </row>
-    <row r="387" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C387" s="14"/>
       <c r="L387" s="14"/>
     </row>
-    <row r="388" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C388" s="14"/>
       <c r="L388" s="14"/>
     </row>
-    <row r="389" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C389" s="14"/>
       <c r="L389" s="14"/>
     </row>
-    <row r="390" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C390" s="14"/>
       <c r="L390" s="14"/>
     </row>
-    <row r="391" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C391" s="14"/>
       <c r="L391" s="14"/>
     </row>
-    <row r="392" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C392" s="14"/>
       <c r="L392" s="14"/>
     </row>
-    <row r="393" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C393" s="14"/>
       <c r="L393" s="14"/>
     </row>
-    <row r="394" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C394" s="14"/>
       <c r="L394" s="14"/>
     </row>
-    <row r="395" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C395" s="14"/>
       <c r="L395" s="14"/>
     </row>
-    <row r="396" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C396" s="14"/>
       <c r="L396" s="14"/>
     </row>
-    <row r="397" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C397" s="14"/>
       <c r="L397" s="14"/>
     </row>
-    <row r="398" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C398" s="14"/>
       <c r="L398" s="14"/>
     </row>
-    <row r="399" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C399" s="14"/>
       <c r="L399" s="14"/>
     </row>
-    <row r="400" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C400" s="14"/>
       <c r="L400" s="14"/>
     </row>
-    <row r="401" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C401" s="14"/>
       <c r="L401" s="14"/>
     </row>
-    <row r="402" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C402" s="14"/>
       <c r="L402" s="14"/>
     </row>
-    <row r="403" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C403" s="14"/>
       <c r="L403" s="14"/>
     </row>
-    <row r="404" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C404" s="14"/>
       <c r="L404" s="14"/>
     </row>
-    <row r="405" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C405" s="14"/>
       <c r="L405" s="14"/>
     </row>
-    <row r="406" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C406" s="14"/>
       <c r="L406" s="14"/>
     </row>
-    <row r="407" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C407" s="14"/>
       <c r="L407" s="14"/>
     </row>
-    <row r="408" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C408" s="14"/>
       <c r="L408" s="14"/>
     </row>
-    <row r="409" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C409" s="14"/>
       <c r="L409" s="14"/>
     </row>
-    <row r="410" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C410" s="14"/>
       <c r="L410" s="14"/>
     </row>
-    <row r="411" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C411" s="14"/>
       <c r="L411" s="14"/>
     </row>
-    <row r="412" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C412" s="14"/>
       <c r="L412" s="14"/>
     </row>
-    <row r="413" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C413" s="14"/>
       <c r="L413" s="14"/>
     </row>
-    <row r="414" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C414" s="14"/>
       <c r="L414" s="14"/>
     </row>
-    <row r="415" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C415" s="14"/>
       <c r="L415" s="14"/>
     </row>
-    <row r="416" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C416" s="14"/>
       <c r="L416" s="14"/>
     </row>
-    <row r="417" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C417" s="14"/>
       <c r="L417" s="14"/>
     </row>
-    <row r="418" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C418" s="14"/>
       <c r="L418" s="14"/>
     </row>
-    <row r="419" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C419" s="14"/>
       <c r="L419" s="14"/>
     </row>
-    <row r="420" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C420" s="14"/>
       <c r="L420" s="14"/>
     </row>
-    <row r="421" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C421" s="14"/>
       <c r="L421" s="14"/>
     </row>
-    <row r="422" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C422" s="14"/>
       <c r="L422" s="14"/>
     </row>
-    <row r="423" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C423" s="14"/>
       <c r="L423" s="14"/>
     </row>
-    <row r="424" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C424" s="14"/>
       <c r="L424" s="14"/>
     </row>
-    <row r="425" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C425" s="14"/>
       <c r="L425" s="14"/>
     </row>
-    <row r="426" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C426" s="14"/>
       <c r="L426" s="14"/>
     </row>
-    <row r="427" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C427" s="14"/>
       <c r="L427" s="14"/>
     </row>
-    <row r="428" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C428" s="14"/>
       <c r="L428" s="14"/>
     </row>
-    <row r="429" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C429" s="14"/>
       <c r="L429" s="14"/>
     </row>
-    <row r="430" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C430" s="14"/>
       <c r="L430" s="14"/>
     </row>
-    <row r="431" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C431" s="14"/>
       <c r="L431" s="14"/>
     </row>
-    <row r="432" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C432" s="14"/>
       <c r="L432" s="14"/>
     </row>
-    <row r="433" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C433" s="14"/>
       <c r="L433" s="14"/>
     </row>
-    <row r="434" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C434" s="14"/>
       <c r="L434" s="14"/>
     </row>
-    <row r="435" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C435" s="14"/>
       <c r="L435" s="14"/>
     </row>
-    <row r="436" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C436" s="14"/>
       <c r="L436" s="14"/>
     </row>
-    <row r="437" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C437" s="14"/>
       <c r="L437" s="14"/>
     </row>
-    <row r="438" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C438" s="14"/>
       <c r="L438" s="14"/>
     </row>
-    <row r="439" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C439" s="14"/>
       <c r="L439" s="14"/>
     </row>
-    <row r="440" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C440" s="14"/>
       <c r="L440" s="14"/>
     </row>
-    <row r="441" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C441" s="14"/>
       <c r="L441" s="14"/>
     </row>
-    <row r="442" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C442" s="14"/>
       <c r="L442" s="14"/>
     </row>
-    <row r="443" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C443" s="14"/>
       <c r="L443" s="14"/>
     </row>
-    <row r="444" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C444" s="14"/>
       <c r="L444" s="14"/>
     </row>
-    <row r="445" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C445" s="14"/>
       <c r="L445" s="14"/>
     </row>
-    <row r="446" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C446" s="14"/>
       <c r="L446" s="14"/>
     </row>
-    <row r="447" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C447" s="14"/>
       <c r="L447" s="14"/>
     </row>
-    <row r="448" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C448" s="14"/>
       <c r="L448" s="14"/>
     </row>
-    <row r="449" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C449" s="14"/>
       <c r="L449" s="14"/>
     </row>
-    <row r="450" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C450" s="14"/>
       <c r="L450" s="14"/>
     </row>
-    <row r="451" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C451" s="14"/>
       <c r="L451" s="14"/>
     </row>
-    <row r="452" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C452" s="14"/>
       <c r="L452" s="14"/>
     </row>
-    <row r="453" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C453" s="14"/>
       <c r="L453" s="14"/>
     </row>
-    <row r="454" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C454" s="14"/>
       <c r="L454" s="14"/>
     </row>
-    <row r="455" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C455" s="14"/>
       <c r="L455" s="14"/>
     </row>
-    <row r="456" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C456" s="14"/>
       <c r="L456" s="14"/>
     </row>
-    <row r="457" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C457" s="14"/>
       <c r="L457" s="14"/>
     </row>
-    <row r="458" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C458" s="14"/>
       <c r="L458" s="14"/>
     </row>
-    <row r="459" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C459" s="14"/>
       <c r="L459" s="14"/>
     </row>
-    <row r="460" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C460" s="14"/>
       <c r="L460" s="14"/>
     </row>
-    <row r="461" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C461" s="14"/>
       <c r="L461" s="14"/>
     </row>
-    <row r="462" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C462" s="14"/>
       <c r="L462" s="14"/>
     </row>
-    <row r="463" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C463" s="14"/>
       <c r="L463" s="14"/>
     </row>
-    <row r="464" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C464" s="14"/>
       <c r="L464" s="14"/>
     </row>
-    <row r="465" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C465" s="14"/>
       <c r="L465" s="14"/>
     </row>
-    <row r="466" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C466" s="14"/>
       <c r="L466" s="14"/>
     </row>
-    <row r="467" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C467" s="14"/>
       <c r="L467" s="14"/>
     </row>
-    <row r="468" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C468" s="14"/>
       <c r="L468" s="14"/>
     </row>
-    <row r="469" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C469" s="14"/>
       <c r="L469" s="14"/>
     </row>
-    <row r="470" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C470" s="14"/>
       <c r="L470" s="14"/>
     </row>
-    <row r="471" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C471" s="14"/>
       <c r="L471" s="14"/>
     </row>
-    <row r="472" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C472" s="14"/>
       <c r="L472" s="14"/>
     </row>
-    <row r="473" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C473" s="14"/>
       <c r="L473" s="14"/>
     </row>
-    <row r="474" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C474" s="14"/>
       <c r="L474" s="14"/>
     </row>
-    <row r="475" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C475" s="14"/>
       <c r="L475" s="14"/>
     </row>
-    <row r="476" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C476" s="14"/>
       <c r="L476" s="14"/>
     </row>
-    <row r="477" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C477" s="14"/>
       <c r="L477" s="14"/>
     </row>
-    <row r="478" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C478" s="14"/>
       <c r="L478" s="14"/>
     </row>
-    <row r="479" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C479" s="14"/>
       <c r="L479" s="14"/>
     </row>
-    <row r="480" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C480" s="14"/>
       <c r="L480" s="14"/>
     </row>
-    <row r="481" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C481" s="14"/>
       <c r="L481" s="14"/>
     </row>
-    <row r="482" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C482" s="14"/>
       <c r="L482" s="14"/>
     </row>
-    <row r="483" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C483" s="14"/>
       <c r="L483" s="14"/>
     </row>
-    <row r="484" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C484" s="14"/>
       <c r="L484" s="14"/>
     </row>
-    <row r="485" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C485" s="14"/>
       <c r="L485" s="14"/>
     </row>
-    <row r="486" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C486" s="14"/>
       <c r="L486" s="14"/>
     </row>
-    <row r="487" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C487" s="14"/>
       <c r="L487" s="14"/>
     </row>
-    <row r="488" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C488" s="14"/>
       <c r="L488" s="14"/>
     </row>
-    <row r="489" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C489" s="14"/>
       <c r="L489" s="14"/>
     </row>
-    <row r="490" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C490" s="14"/>
       <c r="L490" s="14"/>
     </row>
-    <row r="491" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C491" s="14"/>
       <c r="L491" s="14"/>
     </row>
-    <row r="492" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C492" s="14"/>
       <c r="L492" s="14"/>
     </row>
-    <row r="493" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C493" s="14"/>
       <c r="L493" s="14"/>
     </row>
-    <row r="494" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C494" s="14"/>
       <c r="L494" s="14"/>
     </row>
-    <row r="495" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C495" s="14"/>
       <c r="L495" s="14"/>
     </row>
-    <row r="496" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C496" s="14"/>
       <c r="L496" s="14"/>
     </row>
-    <row r="497" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C497" s="14"/>
       <c r="L497" s="14"/>
     </row>
-    <row r="498" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C498" s="14"/>
       <c r="L498" s="14"/>
     </row>
-    <row r="499" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C499" s="14"/>
       <c r="L499" s="14"/>
     </row>
-    <row r="500" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C500" s="14"/>
       <c r="L500" s="14"/>
     </row>
-    <row r="501" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C501" s="14"/>
       <c r="L501" s="14"/>
     </row>
-    <row r="502" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C502" s="14"/>
       <c r="L502" s="14"/>
     </row>
-    <row r="503" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C503" s="14"/>
       <c r="L503" s="14"/>
     </row>
-    <row r="504" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C504" s="14"/>
       <c r="L504" s="14"/>
     </row>
-    <row r="505" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C505" s="14"/>
       <c r="L505" s="14"/>
     </row>
-    <row r="506" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C506" s="14"/>
       <c r="L506" s="14"/>
     </row>
-    <row r="507" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C507" s="14"/>
       <c r="L507" s="14"/>
     </row>
-    <row r="508" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C508" s="14"/>
       <c r="L508" s="14"/>
     </row>
-    <row r="509" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C509" s="14"/>
       <c r="L509" s="14"/>
     </row>
-    <row r="510" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C510" s="14"/>
       <c r="L510" s="14"/>
     </row>
-    <row r="511" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C511" s="14"/>
       <c r="L511" s="14"/>
     </row>
-    <row r="512" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C512" s="14"/>
       <c r="L512" s="14"/>
     </row>
-    <row r="513" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C513" s="14"/>
       <c r="L513" s="14"/>
     </row>
-    <row r="514" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C514" s="14"/>
       <c r="L514" s="14"/>
     </row>
-    <row r="515" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C515" s="14"/>
       <c r="L515" s="14"/>
     </row>
-    <row r="516" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C516" s="14"/>
       <c r="L516" s="14"/>
     </row>
-    <row r="517" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C517" s="14"/>
       <c r="L517" s="14"/>
     </row>
-    <row r="518" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C518" s="14"/>
       <c r="L518" s="14"/>
     </row>
-    <row r="519" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C519" s="14"/>
       <c r="L519" s="14"/>
     </row>
-    <row r="520" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C520" s="14"/>
       <c r="L520" s="14"/>
     </row>
-    <row r="521" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C521" s="14"/>
       <c r="L521" s="14"/>
     </row>
-    <row r="522" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C522" s="14"/>
       <c r="L522" s="14"/>
     </row>
-    <row r="523" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C523" s="14"/>
       <c r="L523" s="14"/>
     </row>
-    <row r="524" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C524" s="14"/>
       <c r="L524" s="14"/>
     </row>
-    <row r="525" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C525" s="14"/>
       <c r="L525" s="14"/>
     </row>
-    <row r="526" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C526" s="14"/>
       <c r="L526" s="14"/>
     </row>
-    <row r="527" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C527" s="14"/>
       <c r="L527" s="14"/>
     </row>
-    <row r="528" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C528" s="14"/>
       <c r="L528" s="14"/>
     </row>
-    <row r="529" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C529" s="14"/>
       <c r="L529" s="14"/>
     </row>
-    <row r="530" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C530" s="14"/>
       <c r="L530" s="14"/>
     </row>
-    <row r="531" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C531" s="14"/>
       <c r="L531" s="14"/>
     </row>
-    <row r="532" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C532" s="14"/>
       <c r="L532" s="14"/>
     </row>
-    <row r="533" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C533" s="14"/>
       <c r="L533" s="14"/>
     </row>
-    <row r="534" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C534" s="14"/>
       <c r="L534" s="14"/>
     </row>
-    <row r="535" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C535" s="14"/>
       <c r="L535" s="14"/>
     </row>
-    <row r="536" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C536" s="14"/>
       <c r="L536" s="14"/>
     </row>
-    <row r="537" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C537" s="14"/>
       <c r="L537" s="14"/>
     </row>
-    <row r="538" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C538" s="14"/>
       <c r="L538" s="14"/>
     </row>
-    <row r="539" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C539" s="14"/>
       <c r="L539" s="14"/>
     </row>
-    <row r="540" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C540" s="14"/>
       <c r="L540" s="14"/>
     </row>
-    <row r="541" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C541" s="14"/>
       <c r="L541" s="14"/>
     </row>
-    <row r="542" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C542" s="14"/>
       <c r="L542" s="14"/>
     </row>
-    <row r="543" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C543" s="14"/>
       <c r="L543" s="14"/>
     </row>
-    <row r="544" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C544" s="14"/>
       <c r="L544" s="14"/>
     </row>
-    <row r="545" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C545" s="14"/>
       <c r="L545" s="14"/>
     </row>
-    <row r="546" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C546" s="14"/>
       <c r="L546" s="14"/>
     </row>
-    <row r="547" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C547" s="14"/>
       <c r="L547" s="14"/>
     </row>
-    <row r="548" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C548" s="14"/>
       <c r="L548" s="14"/>
     </row>
-    <row r="549" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C549" s="14"/>
       <c r="L549" s="14"/>
     </row>
-    <row r="550" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C550" s="14"/>
       <c r="L550" s="14"/>
     </row>
-    <row r="551" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C551" s="14"/>
       <c r="L551" s="14"/>
     </row>
-    <row r="552" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C552" s="14"/>
       <c r="L552" s="14"/>
     </row>
-    <row r="553" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C553" s="14"/>
       <c r="L553" s="14"/>
     </row>
-    <row r="554" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C554" s="14"/>
       <c r="L554" s="14"/>
     </row>
-    <row r="555" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C555" s="14"/>
       <c r="L555" s="14"/>
     </row>
-    <row r="556" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C556" s="14"/>
       <c r="L556" s="14"/>
     </row>
-    <row r="557" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C557" s="14"/>
       <c r="L557" s="14"/>
     </row>
-    <row r="558" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C558" s="14"/>
       <c r="L558" s="14"/>
     </row>
-    <row r="559" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C559" s="14"/>
       <c r="L559" s="14"/>
     </row>
-    <row r="560" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C560" s="14"/>
       <c r="L560" s="14"/>
     </row>
-    <row r="561" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C561" s="14"/>
       <c r="L561" s="14"/>
     </row>
-    <row r="562" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C562" s="14"/>
       <c r="L562" s="14"/>
     </row>
-    <row r="563" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C563" s="14"/>
       <c r="L563" s="14"/>
     </row>
-    <row r="564" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C564" s="14"/>
       <c r="L564" s="14"/>
     </row>
-    <row r="565" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C565" s="14"/>
       <c r="L565" s="14"/>
     </row>
-    <row r="566" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C566" s="14"/>
       <c r="L566" s="14"/>
     </row>
-    <row r="567" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C567" s="14"/>
       <c r="L567" s="14"/>
     </row>
-    <row r="568" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C568" s="14"/>
       <c r="L568" s="14"/>
     </row>
-    <row r="569" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C569" s="14"/>
       <c r="L569" s="14"/>
     </row>
-    <row r="570" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C570" s="14"/>
       <c r="L570" s="14"/>
     </row>
-    <row r="571" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C571" s="14"/>
       <c r="L571" s="14"/>
     </row>
-    <row r="572" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C572" s="14"/>
       <c r="L572" s="14"/>
     </row>
-    <row r="573" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C573" s="14"/>
       <c r="L573" s="14"/>
     </row>
-    <row r="574" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C574" s="14"/>
       <c r="L574" s="14"/>
     </row>
-    <row r="575" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C575" s="14"/>
       <c r="L575" s="14"/>
     </row>
-    <row r="576" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C576" s="14"/>
       <c r="L576" s="14"/>
     </row>
-    <row r="577" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C577" s="14"/>
       <c r="L577" s="14"/>
     </row>
-    <row r="578" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C578" s="14"/>
       <c r="L578" s="14"/>
     </row>
-    <row r="579" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C579" s="14"/>
       <c r="L579" s="14"/>
     </row>
-    <row r="580" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C580" s="14"/>
       <c r="L580" s="14"/>
     </row>
-    <row r="581" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C581" s="14"/>
       <c r="L581" s="14"/>
     </row>
-    <row r="582" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C582" s="14"/>
       <c r="L582" s="14"/>
     </row>
-    <row r="583" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C583" s="14"/>
       <c r="L583" s="14"/>
     </row>
-    <row r="584" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C584" s="14"/>
       <c r="L584" s="14"/>
     </row>
-    <row r="585" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C585" s="14"/>
       <c r="L585" s="14"/>
     </row>
-    <row r="586" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C586" s="14"/>
       <c r="L586" s="14"/>
     </row>
-    <row r="587" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C587" s="14"/>
       <c r="L587" s="14"/>
     </row>
-    <row r="588" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C588" s="14"/>
       <c r="L588" s="14"/>
     </row>
-    <row r="589" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C589" s="14"/>
       <c r="L589" s="14"/>
     </row>
-    <row r="590" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C590" s="14"/>
       <c r="L590" s="14"/>
     </row>
-    <row r="591" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C591" s="14"/>
       <c r="L591" s="14"/>
     </row>
-    <row r="592" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C592" s="14"/>
       <c r="L592" s="14"/>
     </row>
-    <row r="593" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C593" s="14"/>
       <c r="L593" s="14"/>
     </row>
-    <row r="594" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C594" s="14"/>
       <c r="L594" s="14"/>
     </row>
-    <row r="595" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C595" s="14"/>
       <c r="L595" s="14"/>
     </row>
-    <row r="596" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C596" s="14"/>
       <c r="L596" s="14"/>
     </row>
-    <row r="597" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C597" s="14"/>
       <c r="L597" s="14"/>
     </row>
-    <row r="598" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C598" s="14"/>
       <c r="L598" s="14"/>
     </row>
-    <row r="599" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C599" s="14"/>
       <c r="L599" s="14"/>
     </row>
-    <row r="600" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C600" s="14"/>
       <c r="L600" s="14"/>
     </row>
-    <row r="601" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C601" s="14"/>
       <c r="L601" s="14"/>
     </row>
-    <row r="602" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C602" s="14"/>
       <c r="L602" s="14"/>
     </row>
-    <row r="603" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C603" s="14"/>
       <c r="L603" s="14"/>
     </row>
-    <row r="604" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C604" s="14"/>
       <c r="L604" s="14"/>
     </row>
-    <row r="605" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C605" s="14"/>
       <c r="L605" s="14"/>
     </row>
-    <row r="606" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C606" s="14"/>
       <c r="L606" s="14"/>
     </row>
-    <row r="607" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C607" s="14"/>
       <c r="L607" s="14"/>
     </row>
-    <row r="608" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C608" s="14"/>
       <c r="L608" s="14"/>
     </row>
-    <row r="609" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C609" s="14"/>
       <c r="L609" s="14"/>
     </row>
-    <row r="610" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C610" s="14"/>
       <c r="L610" s="14"/>
     </row>
-    <row r="611" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C611" s="14"/>
       <c r="L611" s="14"/>
     </row>
-    <row r="612" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C612" s="14"/>
       <c r="L612" s="14"/>
     </row>
-    <row r="613" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C613" s="14"/>
       <c r="L613" s="14"/>
     </row>
-    <row r="614" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C614" s="14"/>
       <c r="L614" s="14"/>
     </row>
-    <row r="615" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C615" s="14"/>
       <c r="L615" s="14"/>
     </row>
-    <row r="616" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C616" s="14"/>
       <c r="L616" s="14"/>
     </row>
-    <row r="617" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C617" s="14"/>
       <c r="L617" s="14"/>
     </row>
-    <row r="618" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C618" s="14"/>
       <c r="L618" s="14"/>
     </row>
-    <row r="619" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C619" s="14"/>
       <c r="L619" s="14"/>
     </row>
-    <row r="620" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C620" s="14"/>
       <c r="L620" s="14"/>
     </row>
-    <row r="621" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C621" s="14"/>
       <c r="L621" s="14"/>
     </row>
-    <row r="622" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C622" s="14"/>
       <c r="L622" s="14"/>
     </row>
-    <row r="623" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C623" s="14"/>
       <c r="L623" s="14"/>
     </row>
-    <row r="624" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C624" s="14"/>
       <c r="L624" s="14"/>
     </row>
-    <row r="625" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C625" s="14"/>
       <c r="L625" s="14"/>
     </row>
-    <row r="626" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C626" s="14"/>
       <c r="L626" s="14"/>
     </row>
-    <row r="627" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C627" s="14"/>
       <c r="L627" s="14"/>
     </row>
-    <row r="628" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C628" s="14"/>
       <c r="L628" s="14"/>
     </row>
-    <row r="629" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C629" s="14"/>
       <c r="L629" s="14"/>
     </row>
-    <row r="630" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C630" s="14"/>
       <c r="L630" s="14"/>
     </row>
-    <row r="631" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C631" s="14"/>
       <c r="L631" s="14"/>
     </row>
-    <row r="632" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C632" s="14"/>
       <c r="L632" s="14"/>
     </row>
-    <row r="633" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C633" s="14"/>
       <c r="L633" s="14"/>
     </row>
-    <row r="634" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C634" s="14"/>
       <c r="L634" s="14"/>
     </row>
-    <row r="635" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C635" s="14"/>
       <c r="L635" s="14"/>
     </row>
-    <row r="636" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C636" s="14"/>
       <c r="L636" s="14"/>
     </row>
-    <row r="637" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C637" s="14"/>
       <c r="L637" s="14"/>
     </row>
-    <row r="638" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C638" s="14"/>
       <c r="L638" s="14"/>
     </row>
-    <row r="639" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C639" s="14"/>
       <c r="L639" s="14"/>
     </row>
-    <row r="640" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C640" s="14"/>
       <c r="L640" s="14"/>
     </row>
-    <row r="641" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C641" s="14"/>
       <c r="L641" s="14"/>
     </row>
-    <row r="642" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C642" s="14"/>
       <c r="L642" s="14"/>
     </row>
-    <row r="643" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C643" s="14"/>
       <c r="L643" s="14"/>
     </row>
-    <row r="644" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C644" s="14"/>
       <c r="L644" s="14"/>
     </row>
-    <row r="645" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C645" s="14"/>
       <c r="L645" s="14"/>
     </row>
-    <row r="646" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C646" s="14"/>
       <c r="L646" s="14"/>
     </row>
-    <row r="647" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C647" s="14"/>
       <c r="L647" s="14"/>
     </row>
-    <row r="648" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C648" s="14"/>
       <c r="L648" s="14"/>
     </row>
-    <row r="649" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C649" s="14"/>
       <c r="L649" s="14"/>
     </row>
-    <row r="650" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C650" s="14"/>
       <c r="L650" s="14"/>
     </row>
-    <row r="651" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C651" s="14"/>
       <c r="L651" s="14"/>
     </row>
-    <row r="652" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C652" s="14"/>
       <c r="L652" s="14"/>
     </row>
-    <row r="653" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C653" s="14"/>
       <c r="L653" s="14"/>
     </row>
-    <row r="654" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C654" s="14"/>
       <c r="L654" s="14"/>
     </row>
-    <row r="655" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C655" s="14"/>
       <c r="L655" s="14"/>
     </row>
-    <row r="656" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C656" s="14"/>
       <c r="L656" s="14"/>
     </row>
-    <row r="657" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C657" s="14"/>
       <c r="L657" s="14"/>
     </row>
-    <row r="658" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C658" s="14"/>
       <c r="L658" s="14"/>
     </row>
-    <row r="659" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C659" s="14"/>
       <c r="L659" s="14"/>
     </row>
-    <row r="660" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C660" s="14"/>
       <c r="L660" s="14"/>
     </row>
-    <row r="661" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C661" s="14"/>
       <c r="L661" s="14"/>
     </row>
-    <row r="662" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C662" s="14"/>
       <c r="L662" s="14"/>
     </row>
-    <row r="663" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C663" s="14"/>
       <c r="L663" s="14"/>
     </row>
-    <row r="664" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C664" s="14"/>
       <c r="L664" s="14"/>
     </row>
-    <row r="665" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C665" s="14"/>
       <c r="L665" s="14"/>
     </row>
-    <row r="666" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C666" s="14"/>
       <c r="L666" s="14"/>
     </row>
-    <row r="667" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C667" s="14"/>
       <c r="L667" s="14"/>
     </row>
-    <row r="668" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C668" s="14"/>
       <c r="L668" s="14"/>
     </row>
-    <row r="669" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C669" s="14"/>
       <c r="L669" s="14"/>
     </row>
-    <row r="670" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C670" s="14"/>
       <c r="L670" s="14"/>
     </row>
-    <row r="671" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C671" s="14"/>
       <c r="L671" s="14"/>
     </row>
-    <row r="672" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C672" s="14"/>
       <c r="L672" s="14"/>
     </row>
-    <row r="673" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C673" s="14"/>
       <c r="L673" s="14"/>
     </row>
-    <row r="674" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C674" s="14"/>
       <c r="L674" s="14"/>
     </row>
-    <row r="675" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C675" s="14"/>
       <c r="L675" s="14"/>
     </row>
-    <row r="676" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C676" s="14"/>
       <c r="L676" s="14"/>
     </row>
-    <row r="677" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C677" s="14"/>
       <c r="L677" s="14"/>
     </row>
-    <row r="678" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C678" s="14"/>
       <c r="L678" s="14"/>
     </row>
-    <row r="679" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C679" s="14"/>
       <c r="L679" s="14"/>
     </row>
-    <row r="680" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C680" s="14"/>
       <c r="L680" s="14"/>
     </row>
-    <row r="681" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C681" s="14"/>
       <c r="L681" s="14"/>
     </row>
-    <row r="682" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C682" s="14"/>
       <c r="L682" s="14"/>
     </row>
-    <row r="683" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C683" s="14"/>
       <c r="L683" s="14"/>
     </row>
-    <row r="684" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C684" s="14"/>
       <c r="L684" s="14"/>
     </row>
-    <row r="685" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C685" s="14"/>
       <c r="L685" s="14"/>
     </row>
-    <row r="686" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C686" s="14"/>
       <c r="L686" s="14"/>
     </row>
-    <row r="687" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C687" s="14"/>
       <c r="L687" s="14"/>
     </row>
-    <row r="688" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C688" s="14"/>
       <c r="L688" s="14"/>
     </row>
-    <row r="689" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C689" s="14"/>
       <c r="L689" s="14"/>
     </row>
-    <row r="690" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C690" s="14"/>
       <c r="L690" s="14"/>
     </row>
-    <row r="691" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C691" s="14"/>
       <c r="L691" s="14"/>
     </row>
-    <row r="692" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C692" s="14"/>
       <c r="L692" s="14"/>
     </row>
-    <row r="693" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C693" s="14"/>
       <c r="L693" s="14"/>
     </row>
-    <row r="694" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C694" s="14"/>
       <c r="L694" s="14"/>
     </row>
-    <row r="695" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C695" s="14"/>
       <c r="L695" s="14"/>
     </row>
-    <row r="696" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C696" s="14"/>
       <c r="L696" s="14"/>
     </row>
-    <row r="697" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C697" s="14"/>
       <c r="L697" s="14"/>
     </row>
-    <row r="698" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C698" s="14"/>
       <c r="L698" s="14"/>
     </row>
-    <row r="699" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C699" s="14"/>
       <c r="L699" s="14"/>
     </row>
-    <row r="700" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C700" s="14"/>
       <c r="L700" s="14"/>
     </row>
-    <row r="701" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C701" s="14"/>
       <c r="L701" s="14"/>
     </row>
-    <row r="702" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C702" s="14"/>
       <c r="L702" s="14"/>
     </row>
-    <row r="703" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C703" s="14"/>
       <c r="L703" s="14"/>
     </row>
-    <row r="704" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C704" s="14"/>
       <c r="L704" s="14"/>
     </row>
-    <row r="705" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C705" s="14"/>
       <c r="L705" s="14"/>
     </row>
-    <row r="706" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C706" s="14"/>
       <c r="L706" s="14"/>
     </row>
-    <row r="707" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C707" s="14"/>
       <c r="L707" s="14"/>
     </row>
-    <row r="708" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C708" s="14"/>
       <c r="L708" s="14"/>
     </row>
-    <row r="709" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C709" s="14"/>
       <c r="L709" s="14"/>
     </row>
-    <row r="710" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C710" s="14"/>
       <c r="L710" s="14"/>
     </row>
-    <row r="711" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C711" s="14"/>
       <c r="L711" s="14"/>
     </row>
-    <row r="712" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C712" s="14"/>
       <c r="L712" s="14"/>
     </row>
-    <row r="713" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C713" s="14"/>
       <c r="L713" s="14"/>
     </row>
-    <row r="714" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C714" s="14"/>
       <c r="L714" s="14"/>
     </row>
-    <row r="715" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C715" s="14"/>
       <c r="L715" s="14"/>
     </row>
-    <row r="716" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C716" s="14"/>
       <c r="L716" s="14"/>
     </row>
-    <row r="717" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C717" s="14"/>
       <c r="L717" s="14"/>
     </row>
-    <row r="718" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C718" s="14"/>
       <c r="L718" s="14"/>
     </row>
-    <row r="719" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C719" s="14"/>
       <c r="L719" s="14"/>
     </row>
-    <row r="720" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C720" s="14"/>
       <c r="L720" s="14"/>
     </row>
-    <row r="721" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C721" s="14"/>
       <c r="L721" s="14"/>
     </row>
-    <row r="722" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C722" s="14"/>
       <c r="L722" s="14"/>
     </row>
-    <row r="723" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C723" s="14"/>
       <c r="L723" s="14"/>
     </row>
-    <row r="724" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C724" s="14"/>
       <c r="L724" s="14"/>
     </row>
-    <row r="725" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C725" s="14"/>
       <c r="L725" s="14"/>
     </row>
-    <row r="726" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C726" s="14"/>
       <c r="L726" s="14"/>
     </row>
-    <row r="727" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C727" s="14"/>
       <c r="L727" s="14"/>
     </row>
-    <row r="728" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C728" s="14"/>
       <c r="L728" s="14"/>
     </row>
-    <row r="729" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C729" s="14"/>
       <c r="L729" s="14"/>
     </row>
-    <row r="730" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C730" s="14"/>
       <c r="L730" s="14"/>
     </row>
-    <row r="731" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C731" s="14"/>
       <c r="L731" s="14"/>
     </row>
-    <row r="732" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C732" s="14"/>
       <c r="L732" s="14"/>
     </row>
-    <row r="733" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C733" s="14"/>
       <c r="L733" s="14"/>
     </row>
-    <row r="734" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C734" s="14"/>
       <c r="L734" s="14"/>
     </row>
-    <row r="735" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C735" s="14"/>
       <c r="L735" s="14"/>
     </row>
-    <row r="736" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C736" s="14"/>
       <c r="L736" s="14"/>
     </row>
-    <row r="737" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C737" s="14"/>
       <c r="L737" s="14"/>
     </row>
-    <row r="738" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C738" s="14"/>
       <c r="L738" s="14"/>
     </row>
-    <row r="739" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C739" s="14"/>
       <c r="L739" s="14"/>
     </row>
-    <row r="740" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C740" s="14"/>
       <c r="L740" s="14"/>
     </row>
-    <row r="741" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C741" s="14"/>
       <c r="L741" s="14"/>
     </row>
-    <row r="742" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C742" s="14"/>
       <c r="L742" s="14"/>
     </row>
-    <row r="743" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C743" s="14"/>
       <c r="L743" s="14"/>
     </row>
-    <row r="744" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C744" s="14"/>
       <c r="L744" s="14"/>
     </row>
-    <row r="745" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C745" s="14"/>
       <c r="L745" s="14"/>
     </row>
-    <row r="746" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C746" s="14"/>
       <c r="L746" s="14"/>
     </row>
-    <row r="747" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C747" s="14"/>
       <c r="L747" s="14"/>
     </row>
-    <row r="748" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C748" s="14"/>
       <c r="L748" s="14"/>
     </row>
-    <row r="749" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C749" s="14"/>
       <c r="L749" s="14"/>
     </row>
-    <row r="750" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C750" s="14"/>
       <c r="L750" s="14"/>
     </row>
-    <row r="751" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C751" s="14"/>
       <c r="L751" s="14"/>
     </row>
-    <row r="752" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C752" s="14"/>
       <c r="L752" s="14"/>
     </row>
-    <row r="753" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C753" s="14"/>
       <c r="L753" s="14"/>
     </row>
-    <row r="754" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C754" s="14"/>
       <c r="L754" s="14"/>
     </row>
-    <row r="755" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C755" s="14"/>
       <c r="L755" s="14"/>
     </row>
-    <row r="756" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C756" s="14"/>
       <c r="L756" s="14"/>
     </row>
-    <row r="757" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C757" s="14"/>
       <c r="L757" s="14"/>
     </row>
-    <row r="758" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C758" s="14"/>
       <c r="L758" s="14"/>
     </row>
-    <row r="759" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C759" s="14"/>
       <c r="L759" s="14"/>
     </row>
-    <row r="760" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C760" s="14"/>
       <c r="L760" s="14"/>
     </row>
-    <row r="761" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C761" s="14"/>
       <c r="L761" s="14"/>
     </row>
-    <row r="762" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C762" s="14"/>
       <c r="L762" s="14"/>
     </row>
-    <row r="763" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C763" s="14"/>
       <c r="L763" s="14"/>
     </row>
-    <row r="764" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C764" s="14"/>
       <c r="L764" s="14"/>
     </row>
-    <row r="765" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C765" s="14"/>
       <c r="L765" s="14"/>
     </row>
-    <row r="766" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C766" s="14"/>
       <c r="L766" s="14"/>
     </row>
-    <row r="767" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C767" s="14"/>
       <c r="L767" s="14"/>
     </row>
-    <row r="768" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C768" s="14"/>
       <c r="L768" s="14"/>
     </row>
-    <row r="769" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C769" s="14"/>
       <c r="L769" s="14"/>
     </row>
-    <row r="770" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C770" s="14"/>
       <c r="L770" s="14"/>
     </row>
-    <row r="771" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C771" s="14"/>
       <c r="L771" s="14"/>
     </row>
-    <row r="772" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C772" s="14"/>
       <c r="L772" s="14"/>
     </row>
-    <row r="773" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C773" s="14"/>
       <c r="L773" s="14"/>
     </row>
-    <row r="774" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C774" s="14"/>
       <c r="L774" s="14"/>
     </row>
-    <row r="775" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C775" s="14"/>
       <c r="L775" s="14"/>
     </row>
-    <row r="776" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C776" s="14"/>
       <c r="L776" s="14"/>
     </row>
-    <row r="777" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C777" s="14"/>
       <c r="L777" s="14"/>
     </row>
-    <row r="778" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C778" s="14"/>
       <c r="L778" s="14"/>
     </row>
-    <row r="779" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C779" s="14"/>
       <c r="L779" s="14"/>
     </row>
-    <row r="780" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C780" s="14"/>
       <c r="L780" s="14"/>
     </row>
-    <row r="781" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C781" s="14"/>
       <c r="L781" s="14"/>
     </row>
-    <row r="782" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C782" s="14"/>
       <c r="L782" s="14"/>
     </row>
-    <row r="783" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C783" s="14"/>
       <c r="L783" s="14"/>
     </row>
-    <row r="784" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C784" s="14"/>
       <c r="L784" s="14"/>
     </row>
-    <row r="785" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C785" s="14"/>
       <c r="L785" s="14"/>
     </row>
-    <row r="786" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C786" s="14"/>
       <c r="L786" s="14"/>
     </row>
-    <row r="787" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C787" s="14"/>
       <c r="L787" s="14"/>
     </row>
-    <row r="788" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C788" s="14"/>
       <c r="L788" s="14"/>
     </row>
-    <row r="789" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C789" s="14"/>
       <c r="L789" s="14"/>
     </row>
-    <row r="790" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C790" s="14"/>
       <c r="L790" s="14"/>
     </row>
-    <row r="791" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C791" s="14"/>
       <c r="L791" s="14"/>
     </row>
-    <row r="792" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C792" s="14"/>
       <c r="L792" s="14"/>
     </row>
-    <row r="793" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C793" s="14"/>
       <c r="L793" s="14"/>
     </row>
-    <row r="794" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C794" s="14"/>
       <c r="L794" s="14"/>
     </row>
-    <row r="795" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C795" s="14"/>
       <c r="L795" s="14"/>
     </row>
-    <row r="796" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C796" s="14"/>
       <c r="L796" s="14"/>
     </row>
-    <row r="797" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C797" s="14"/>
       <c r="L797" s="14"/>
     </row>
-    <row r="798" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C798" s="14"/>
       <c r="L798" s="14"/>
     </row>
-    <row r="799" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C799" s="14"/>
       <c r="L799" s="14"/>
     </row>
-    <row r="800" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C800" s="14"/>
       <c r="L800" s="14"/>
     </row>
-    <row r="801" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C801" s="14"/>
       <c r="L801" s="14"/>
     </row>
-    <row r="802" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C802" s="14"/>
       <c r="L802" s="14"/>
     </row>
-    <row r="803" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C803" s="14"/>
       <c r="L803" s="14"/>
     </row>
-    <row r="804" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C804" s="14"/>
       <c r="L804" s="14"/>
     </row>
-    <row r="805" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C805" s="14"/>
       <c r="L805" s="14"/>
     </row>
-    <row r="806" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C806" s="14"/>
       <c r="L806" s="14"/>
     </row>
-    <row r="807" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C807" s="14"/>
       <c r="L807" s="14"/>
     </row>
-    <row r="808" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C808" s="14"/>
       <c r="L808" s="14"/>
     </row>
-    <row r="809" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C809" s="14"/>
       <c r="L809" s="14"/>
     </row>
-    <row r="810" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C810" s="14"/>
       <c r="L810" s="14"/>
     </row>
-    <row r="811" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C811" s="14"/>
       <c r="L811" s="14"/>
     </row>
-    <row r="812" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C812" s="14"/>
       <c r="L812" s="14"/>
     </row>
-    <row r="813" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C813" s="14"/>
       <c r="L813" s="14"/>
     </row>
-    <row r="814" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C814" s="14"/>
       <c r="L814" s="14"/>
     </row>
-    <row r="815" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C815" s="14"/>
       <c r="L815" s="14"/>
     </row>
-    <row r="816" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C816" s="14"/>
       <c r="L816" s="14"/>
     </row>
-    <row r="817" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C817" s="14"/>
       <c r="L817" s="14"/>
     </row>
-    <row r="818" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C818" s="14"/>
       <c r="L818" s="14"/>
     </row>
-    <row r="819" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C819" s="14"/>
       <c r="L819" s="14"/>
     </row>
-    <row r="820" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C820" s="14"/>
       <c r="L820" s="14"/>
     </row>
-    <row r="821" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C821" s="14"/>
       <c r="L821" s="14"/>
     </row>
-    <row r="822" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C822" s="14"/>
       <c r="L822" s="14"/>
     </row>
-    <row r="823" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C823" s="14"/>
       <c r="L823" s="14"/>
     </row>
-    <row r="824" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C824" s="14"/>
       <c r="L824" s="14"/>
     </row>
-    <row r="825" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C825" s="14"/>
       <c r="L825" s="14"/>
     </row>
-    <row r="826" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C826" s="14"/>
       <c r="L826" s="14"/>
     </row>
-    <row r="827" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C827" s="14"/>
       <c r="L827" s="14"/>
     </row>
-    <row r="828" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C828" s="14"/>
       <c r="L828" s="14"/>
     </row>
-    <row r="829" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C829" s="14"/>
       <c r="L829" s="14"/>
     </row>
-    <row r="830" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C830" s="14"/>
       <c r="L830" s="14"/>
     </row>
-    <row r="831" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C831" s="14"/>
       <c r="L831" s="14"/>
     </row>
-    <row r="832" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C832" s="14"/>
       <c r="L832" s="14"/>
     </row>
-    <row r="833" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C833" s="14"/>
       <c r="L833" s="14"/>
     </row>
-    <row r="834" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C834" s="14"/>
       <c r="L834" s="14"/>
     </row>
-    <row r="835" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C835" s="14"/>
       <c r="L835" s="14"/>
     </row>
-    <row r="836" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C836" s="14"/>
       <c r="L836" s="14"/>
     </row>
-    <row r="837" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C837" s="14"/>
       <c r="L837" s="14"/>
     </row>
-    <row r="838" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C838" s="14"/>
       <c r="L838" s="14"/>
     </row>
-    <row r="839" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C839" s="14"/>
       <c r="L839" s="14"/>
     </row>
-    <row r="840" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C840" s="14"/>
       <c r="L840" s="14"/>
     </row>
-    <row r="841" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C841" s="14"/>
       <c r="L841" s="14"/>
     </row>
-    <row r="842" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C842" s="14"/>
       <c r="L842" s="14"/>
     </row>
-    <row r="843" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C843" s="14"/>
       <c r="L843" s="14"/>
     </row>
-    <row r="844" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C844" s="14"/>
       <c r="L844" s="14"/>
     </row>
-    <row r="845" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C845" s="14"/>
       <c r="L845" s="14"/>
     </row>
-    <row r="846" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C846" s="14"/>
       <c r="L846" s="14"/>
     </row>
-    <row r="847" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C847" s="14"/>
       <c r="L847" s="14"/>
     </row>
-    <row r="848" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C848" s="14"/>
       <c r="L848" s="14"/>
     </row>
-    <row r="849" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C849" s="14"/>
       <c r="L849" s="14"/>
     </row>
-    <row r="850" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C850" s="14"/>
       <c r="L850" s="14"/>
     </row>
-    <row r="851" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C851" s="14"/>
       <c r="L851" s="14"/>
     </row>
-    <row r="852" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C852" s="14"/>
       <c r="L852" s="14"/>
     </row>
-    <row r="853" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C853" s="14"/>
       <c r="L853" s="14"/>
     </row>
-    <row r="854" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C854" s="14"/>
       <c r="L854" s="14"/>
     </row>
-    <row r="855" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C855" s="14"/>
       <c r="L855" s="14"/>
     </row>
-    <row r="856" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C856" s="14"/>
       <c r="L856" s="14"/>
     </row>
-    <row r="857" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C857" s="14"/>
       <c r="L857" s="14"/>
     </row>
-    <row r="858" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C858" s="14"/>
       <c r="L858" s="14"/>
     </row>
-    <row r="859" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C859" s="14"/>
       <c r="L859" s="14"/>
     </row>
-    <row r="860" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C860" s="14"/>
       <c r="L860" s="14"/>
     </row>
-    <row r="861" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C861" s="14"/>
       <c r="L861" s="14"/>
     </row>
-    <row r="862" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C862" s="14"/>
       <c r="L862" s="14"/>
     </row>
-    <row r="863" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C863" s="14"/>
       <c r="L863" s="14"/>
     </row>
-    <row r="864" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C864" s="14"/>
       <c r="L864" s="14"/>
     </row>
-    <row r="865" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C865" s="14"/>
       <c r="L865" s="14"/>
     </row>
-    <row r="866" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C866" s="14"/>
       <c r="L866" s="14"/>
     </row>
-    <row r="867" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C867" s="14"/>
       <c r="L867" s="14"/>
     </row>
-    <row r="868" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C868" s="14"/>
       <c r="L868" s="14"/>
     </row>
-    <row r="869" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C869" s="14"/>
       <c r="L869" s="14"/>
     </row>
-    <row r="870" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C870" s="14"/>
       <c r="L870" s="14"/>
     </row>
-    <row r="871" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C871" s="14"/>
       <c r="L871" s="14"/>
     </row>
-    <row r="872" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C872" s="14"/>
       <c r="L872" s="14"/>
     </row>
-    <row r="873" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C873" s="14"/>
       <c r="L873" s="14"/>
     </row>
-    <row r="874" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C874" s="14"/>
       <c r="L874" s="14"/>
     </row>
-    <row r="875" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C875" s="14"/>
       <c r="L875" s="14"/>
     </row>
-    <row r="876" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C876" s="14"/>
       <c r="L876" s="14"/>
     </row>
-    <row r="877" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C877" s="14"/>
       <c r="L877" s="14"/>
     </row>
-    <row r="878" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C878" s="14"/>
       <c r="L878" s="14"/>
     </row>
-    <row r="879" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C879" s="14"/>
       <c r="L879" s="14"/>
     </row>
-    <row r="880" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C880" s="14"/>
       <c r="L880" s="14"/>
     </row>
-    <row r="881" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C881" s="14"/>
       <c r="L881" s="14"/>
     </row>
-    <row r="882" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C882" s="14"/>
       <c r="L882" s="14"/>
     </row>
-    <row r="883" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C883" s="14"/>
       <c r="L883" s="14"/>
     </row>
-    <row r="884" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C884" s="14"/>
       <c r="L884" s="14"/>
     </row>
-    <row r="885" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C885" s="14"/>
       <c r="L885" s="14"/>
     </row>
-    <row r="886" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C886" s="14"/>
       <c r="L886" s="14"/>
     </row>
-    <row r="887" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C887" s="14"/>
       <c r="L887" s="14"/>
     </row>
-    <row r="888" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C888" s="14"/>
       <c r="L888" s="14"/>
     </row>
-    <row r="889" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C889" s="14"/>
       <c r="L889" s="14"/>
     </row>
-    <row r="890" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C890" s="14"/>
       <c r="L890" s="14"/>
     </row>
-    <row r="891" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C891" s="14"/>
       <c r="L891" s="14"/>
     </row>
-    <row r="892" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C892" s="14"/>
       <c r="L892" s="14"/>
     </row>
-    <row r="893" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C893" s="14"/>
       <c r="L893" s="14"/>
     </row>
-    <row r="894" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C894" s="14"/>
       <c r="L894" s="14"/>
     </row>
-    <row r="895" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C895" s="14"/>
       <c r="L895" s="14"/>
     </row>
-    <row r="896" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C896" s="14"/>
       <c r="L896" s="14"/>
     </row>
-    <row r="897" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C897" s="14"/>
       <c r="L897" s="14"/>
     </row>
-    <row r="898" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C898" s="14"/>
       <c r="L898" s="14"/>
     </row>
-    <row r="899" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C899" s="14"/>
       <c r="L899" s="14"/>
     </row>
-    <row r="900" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C900" s="14"/>
       <c r="L900" s="14"/>
     </row>
-    <row r="901" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C901" s="14"/>
       <c r="L901" s="14"/>
     </row>
-    <row r="902" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C902" s="14"/>
       <c r="L902" s="14"/>
     </row>
-    <row r="903" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C903" s="14"/>
       <c r="L903" s="14"/>
     </row>
-    <row r="904" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C904" s="14"/>
       <c r="L904" s="14"/>
     </row>
-    <row r="905" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C905" s="14"/>
       <c r="L905" s="14"/>
     </row>
-    <row r="906" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C906" s="14"/>
       <c r="L906" s="14"/>
     </row>
-    <row r="907" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C907" s="14"/>
       <c r="L907" s="14"/>
     </row>
-    <row r="908" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C908" s="14"/>
       <c r="L908" s="14"/>
     </row>
-    <row r="909" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C909" s="14"/>
       <c r="L909" s="14"/>
     </row>
-    <row r="910" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C910" s="14"/>
       <c r="L910" s="14"/>
     </row>
-    <row r="911" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C911" s="14"/>
       <c r="L911" s="14"/>
     </row>
-    <row r="912" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C912" s="14"/>
       <c r="L912" s="14"/>
     </row>
-    <row r="913" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C913" s="14"/>
       <c r="L913" s="14"/>
     </row>
-    <row r="914" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C914" s="14"/>
       <c r="L914" s="14"/>
     </row>
-    <row r="915" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C915" s="14"/>
       <c r="L915" s="14"/>
     </row>
-    <row r="916" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C916" s="14"/>
       <c r="L916" s="14"/>
     </row>
-    <row r="917" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C917" s="14"/>
       <c r="L917" s="14"/>
     </row>
-    <row r="918" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C918" s="14"/>
       <c r="L918" s="14"/>
     </row>
-    <row r="919" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C919" s="14"/>
       <c r="L919" s="14"/>
     </row>
-    <row r="920" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C920" s="14"/>
       <c r="L920" s="14"/>
     </row>
-    <row r="921" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C921" s="14"/>
       <c r="L921" s="14"/>
     </row>
-    <row r="922" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C922" s="14"/>
       <c r="L922" s="14"/>
     </row>
-    <row r="923" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C923" s="14"/>
       <c r="L923" s="14"/>
     </row>
-    <row r="924" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C924" s="14"/>
       <c r="L924" s="14"/>
     </row>
-    <row r="925" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C925" s="14"/>
       <c r="L925" s="14"/>
     </row>
-    <row r="926" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C926" s="14"/>
       <c r="L926" s="14"/>
     </row>
-    <row r="927" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C927" s="14"/>
       <c r="L927" s="14"/>
     </row>
-    <row r="928" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C928" s="14"/>
       <c r="L928" s="14"/>
     </row>
-    <row r="929" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C929" s="14"/>
       <c r="L929" s="14"/>
     </row>
-    <row r="930" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C930" s="14"/>
       <c r="L930" s="14"/>
     </row>
-    <row r="931" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C931" s="14"/>
       <c r="L931" s="14"/>
     </row>
-    <row r="932" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C932" s="14"/>
       <c r="L932" s="14"/>
     </row>
-    <row r="933" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C933" s="14"/>
       <c r="L933" s="14"/>
     </row>
-    <row r="934" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C934" s="14"/>
       <c r="L934" s="14"/>
     </row>
-    <row r="935" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C935" s="14"/>
       <c r="L935" s="14"/>
     </row>
-    <row r="936" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C936" s="14"/>
       <c r="L936" s="14"/>
     </row>
-    <row r="937" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C937" s="14"/>
       <c r="L937" s="14"/>
     </row>
-    <row r="938" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C938" s="14"/>
       <c r="L938" s="14"/>
     </row>
-    <row r="939" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C939" s="14"/>
       <c r="L939" s="14"/>
     </row>
-    <row r="940" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C940" s="14"/>
       <c r="L940" s="14"/>
     </row>
-    <row r="941" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C941" s="14"/>
       <c r="L941" s="14"/>
     </row>
-    <row r="942" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C942" s="14"/>
       <c r="L942" s="14"/>
     </row>
-    <row r="943" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C943" s="14"/>
       <c r="L943" s="14"/>
     </row>
-    <row r="944" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C944" s="14"/>
       <c r="L944" s="14"/>
     </row>
-    <row r="945" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C945" s="14"/>
       <c r="L945" s="14"/>
     </row>
-    <row r="946" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C946" s="14"/>
       <c r="L946" s="14"/>
     </row>
-    <row r="947" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C947" s="14"/>
       <c r="L947" s="14"/>
     </row>
-    <row r="948" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C948" s="14"/>
       <c r="L948" s="14"/>
     </row>
-    <row r="949" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C949" s="14"/>
       <c r="L949" s="14"/>
     </row>
-    <row r="950" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C950" s="14"/>
       <c r="L950" s="14"/>
     </row>
-    <row r="951" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C951" s="14"/>
       <c r="L951" s="14"/>
     </row>
-    <row r="952" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C952" s="14"/>
       <c r="L952" s="14"/>
     </row>
-    <row r="953" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C953" s="14"/>
       <c r="L953" s="14"/>
     </row>
-    <row r="954" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C954" s="14"/>
       <c r="L954" s="14"/>
     </row>
-    <row r="955" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C955" s="14"/>
       <c r="L955" s="14"/>
     </row>
-    <row r="956" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C956" s="14"/>
       <c r="L956" s="14"/>
     </row>
-    <row r="957" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C957" s="14"/>
       <c r="L957" s="14"/>
     </row>
-    <row r="958" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C958" s="14"/>
       <c r="L958" s="14"/>
     </row>
-    <row r="959" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C959" s="14"/>
       <c r="L959" s="14"/>
     </row>
-    <row r="960" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C960" s="14"/>
       <c r="L960" s="14"/>
     </row>
-    <row r="961" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C961" s="14"/>
       <c r="L961" s="14"/>
     </row>
-    <row r="962" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C962" s="14"/>
       <c r="L962" s="14"/>
     </row>
-    <row r="963" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C963" s="14"/>
       <c r="L963" s="14"/>
     </row>
-    <row r="964" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C964" s="14"/>
       <c r="L964" s="14"/>
     </row>
-    <row r="965" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C965" s="14"/>
       <c r="L965" s="14"/>
     </row>
-    <row r="966" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C966" s="14"/>
       <c r="L966" s="14"/>
     </row>
-    <row r="967" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C967" s="14"/>
       <c r="L967" s="14"/>
     </row>
-    <row r="968" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C968" s="14"/>
       <c r="L968" s="14"/>
     </row>
-    <row r="969" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C969" s="14"/>
       <c r="L969" s="14"/>
     </row>
-    <row r="970" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C970" s="14"/>
       <c r="L970" s="14"/>
     </row>
-    <row r="971" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C971" s="14"/>
       <c r="L971" s="14"/>
     </row>
-    <row r="972" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C972" s="14"/>
       <c r="L972" s="14"/>
     </row>
-    <row r="973" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C973" s="14"/>
       <c r="L973" s="14"/>
     </row>
-    <row r="974" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C974" s="14"/>
       <c r="L974" s="14"/>
     </row>
-    <row r="975" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C975" s="14"/>
       <c r="L975" s="14"/>
     </row>
-    <row r="976" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C976" s="14"/>
       <c r="L976" s="14"/>
     </row>
-    <row r="977" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C977" s="14"/>
       <c r="L977" s="14"/>
     </row>
-    <row r="978" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C978" s="14"/>
       <c r="L978" s="14"/>
     </row>
-    <row r="979" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C979" s="14"/>
       <c r="L979" s="14"/>
     </row>
-    <row r="980" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C980" s="14"/>
       <c r="L980" s="14"/>
     </row>
-    <row r="981" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C981" s="14"/>
       <c r="L981" s="14"/>
     </row>
-    <row r="982" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C982" s="14"/>
       <c r="L982" s="14"/>
     </row>
-    <row r="983" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C983" s="14"/>
       <c r="L983" s="14"/>
     </row>
-    <row r="984" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C984" s="14"/>
       <c r="L984" s="14"/>
     </row>
-    <row r="985" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C985" s="14"/>
       <c r="L985" s="14"/>
     </row>
-    <row r="986" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C986" s="14"/>
       <c r="L986" s="14"/>
     </row>
-    <row r="987" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C987" s="14"/>
       <c r="L987" s="14"/>
     </row>
-    <row r="988" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C988" s="14"/>
       <c r="L988" s="14"/>
     </row>
-    <row r="989" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C989" s="14"/>
       <c r="L989" s="14"/>
     </row>
-    <row r="990" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C990" s="14"/>
       <c r="L990" s="14"/>
     </row>
-    <row r="991" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C991" s="14"/>
       <c r="L991" s="14"/>
     </row>
-    <row r="992" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C992" s="14"/>
       <c r="L992" s="14"/>
     </row>
-    <row r="993" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C993" s="14"/>
       <c r="L993" s="14"/>
     </row>
-    <row r="994" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C994" s="14"/>
       <c r="L994" s="14"/>
     </row>
-    <row r="995" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C995" s="14"/>
       <c r="L995" s="14"/>
     </row>
-    <row r="996" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C996" s="14"/>
       <c r="L996" s="14"/>
     </row>
-    <row r="997" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C997" s="14"/>
       <c r="L997" s="14"/>
     </row>
-    <row r="998" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C998" s="14"/>
       <c r="L998" s="14"/>
     </row>
-    <row r="999" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C999" s="14"/>
       <c r="L999" s="14"/>
     </row>
-    <row r="1000" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1000" s="14"/>
       <c r="L1000" s="14"/>
     </row>
-    <row r="1001" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1001" s="14"/>
       <c r="L1001" s="14"/>
     </row>
-    <row r="1002" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1002" s="14"/>
       <c r="L1002" s="14"/>
     </row>
-    <row r="1003" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1003" s="14"/>
       <c r="L1003" s="14"/>
     </row>
-    <row r="1004" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1004" s="14"/>
       <c r="L1004" s="14"/>
     </row>
-    <row r="1005" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1005" s="14"/>
       <c r="L1005" s="14"/>
     </row>
-    <row r="1006" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1006" s="14"/>
       <c r="L1006" s="14"/>
     </row>
-    <row r="1007" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1007" s="14"/>
       <c r="L1007" s="14"/>
     </row>
-    <row r="1008" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1008" s="14"/>
       <c r="L1008" s="14"/>
     </row>
-    <row r="1009" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1009" s="14"/>
       <c r="L1009" s="14"/>
     </row>
-    <row r="1010" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1010" s="14"/>
       <c r="L1010" s="14"/>
     </row>
-    <row r="1011" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1011" s="14"/>
       <c r="L1011" s="14"/>
     </row>
-    <row r="1012" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1012" s="14"/>
       <c r="L1012" s="14"/>
     </row>
-    <row r="1013" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1013" s="14"/>
       <c r="L1013" s="14"/>
     </row>
-    <row r="1014" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1014" s="14"/>
       <c r="L1014" s="14"/>
     </row>
-    <row r="1015" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1015" s="14"/>
       <c r="L1015" s="14"/>
     </row>
-    <row r="1016" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1016" s="14"/>
       <c r="L1016" s="14"/>
     </row>
-    <row r="1017" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1017" s="14"/>
       <c r="L1017" s="14"/>
     </row>
-    <row r="1018" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1018" s="14"/>
       <c r="L1018" s="14"/>
     </row>
-    <row r="1019" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1019" s="14"/>
       <c r="L1019" s="14"/>
     </row>
-    <row r="1020" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1020" s="14"/>
       <c r="L1020" s="14"/>
     </row>
-    <row r="1021" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1021" s="14"/>
       <c r="L1021" s="14"/>
     </row>
-    <row r="1022" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1022" s="14"/>
       <c r="L1022" s="14"/>
     </row>
-    <row r="1023" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1023" s="14"/>
       <c r="L1023" s="14"/>
     </row>
-    <row r="1024" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1024" s="14"/>
       <c r="L1024" s="14"/>
     </row>
-    <row r="1025" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1025" s="14"/>
       <c r="L1025" s="14"/>
     </row>
-    <row r="1026" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1026" s="14"/>
       <c r="L1026" s="14"/>
     </row>
-    <row r="1027" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1027" s="14"/>
       <c r="L1027" s="14"/>
     </row>
-    <row r="1028" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1028" s="14"/>
       <c r="L1028" s="14"/>
     </row>
-    <row r="1029" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1029" s="14"/>
       <c r="L1029" s="14"/>
     </row>
-    <row r="1030" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1030" s="14"/>
       <c r="L1030" s="14"/>
     </row>
-    <row r="1031" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1031" s="14"/>
       <c r="L1031" s="14"/>
     </row>
-    <row r="1032" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1032" s="14"/>
       <c r="L1032" s="14"/>
     </row>
-    <row r="1033" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1033" s="14"/>
       <c r="L1033" s="14"/>
     </row>
-    <row r="1034" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1034" s="14"/>
       <c r="L1034" s="14"/>
     </row>
-    <row r="1035" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1035" s="14"/>
       <c r="L1035" s="14"/>
     </row>
-    <row r="1036" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1036" s="14"/>
       <c r="L1036" s="14"/>
     </row>
-    <row r="1037" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1037" s="14"/>
       <c r="L1037" s="14"/>
     </row>
-    <row r="1038" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1038" s="14"/>
       <c r="L1038" s="14"/>
     </row>
-    <row r="1039" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1039" s="14"/>
       <c r="L1039" s="14"/>
     </row>
-    <row r="1040" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1040" s="14"/>
       <c r="L1040" s="14"/>
     </row>
-    <row r="1041" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1041" s="14"/>
       <c r="L1041" s="14"/>
     </row>
-    <row r="1042" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1042" s="14"/>
       <c r="L1042" s="14"/>
     </row>
-    <row r="1043" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1043" s="14"/>
       <c r="L1043" s="14"/>
     </row>
-    <row r="1044" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1044" s="14"/>
       <c r="L1044" s="14"/>
     </row>
-    <row r="1045" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1045" s="14"/>
       <c r="L1045" s="14"/>
     </row>
-    <row r="1046" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1046" s="14"/>
       <c r="L1046" s="14"/>
     </row>
-    <row r="1047" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1047" s="14"/>
       <c r="L1047" s="14"/>
     </row>
-    <row r="1048" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1048" s="14"/>
       <c r="L1048" s="14"/>
     </row>
-    <row r="1049" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1049" s="14"/>
       <c r="L1049" s="14"/>
     </row>
-    <row r="1050" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1050" s="14"/>
       <c r="L1050" s="14"/>
     </row>
-    <row r="1051" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1051" s="14"/>
       <c r="L1051" s="14"/>
     </row>
-    <row r="1052" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1052" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1052" s="14"/>
       <c r="L1052" s="14"/>
     </row>
-    <row r="1053" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1053" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1053" s="14"/>
       <c r="L1053" s="14"/>
     </row>
-    <row r="1054" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1054" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1054" s="14"/>
       <c r="L1054" s="14"/>
     </row>
-    <row r="1055" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1055" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1055" s="14"/>
       <c r="L1055" s="14"/>
     </row>
-    <row r="1056" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1056" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1056" s="14"/>
       <c r="L1056" s="14"/>
     </row>
-    <row r="1057" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1057" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1057" s="14"/>
       <c r="L1057" s="14"/>
     </row>
-    <row r="1058" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1058" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1058" s="14"/>
       <c r="L1058" s="14"/>
     </row>
-    <row r="1059" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1059" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1059" s="14"/>
       <c r="L1059" s="14"/>
     </row>
-    <row r="1060" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1060" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1060" s="14"/>
       <c r="L1060" s="14"/>
     </row>
-    <row r="1061" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1061" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1061" s="14"/>
       <c r="L1061" s="14"/>
     </row>
-    <row r="1062" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1062" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1062" s="14"/>
       <c r="L1062" s="14"/>
     </row>
-    <row r="1063" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1063" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1063" s="14"/>
       <c r="L1063" s="14"/>
     </row>
-    <row r="1064" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1064" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1064" s="14"/>
       <c r="L1064" s="14"/>
     </row>
-    <row r="1065" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1065" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1065" s="14"/>
       <c r="L1065" s="14"/>
     </row>
-    <row r="1066" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1066" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1066" s="14"/>
       <c r="L1066" s="14"/>
     </row>
-    <row r="1067" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1067" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1067" s="14"/>
       <c r="L1067" s="14"/>
     </row>
-    <row r="1068" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1068" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1068" s="14"/>
       <c r="L1068" s="14"/>
     </row>
-    <row r="1069" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1069" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1069" s="14"/>
       <c r="L1069" s="14"/>
     </row>
-    <row r="1070" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1070" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1070" s="14"/>
       <c r="L1070" s="14"/>
     </row>
-    <row r="1071" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1071" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1071" s="14"/>
       <c r="L1071" s="14"/>
     </row>
-    <row r="1072" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1072" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1072" s="14"/>
       <c r="L1072" s="14"/>
     </row>
-    <row r="1073" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1073" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1073" s="14"/>
       <c r="L1073" s="14"/>
     </row>
-    <row r="1074" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1074" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1074" s="14"/>
       <c r="L1074" s="14"/>
     </row>
-    <row r="1075" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1075" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1075" s="14"/>
       <c r="L1075" s="14"/>
     </row>
-    <row r="1076" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1076" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1076" s="14"/>
       <c r="L1076" s="14"/>
     </row>
-    <row r="1077" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1077" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1077" s="14"/>
       <c r="L1077" s="14"/>
     </row>
-    <row r="1078" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1078" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1078" s="14"/>
       <c r="L1078" s="14"/>
     </row>
@@ -11157,14 +11157,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F22F6F-4865-461F-B393-2CB114DD3839}">
   <dimension ref="A1:AT46"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.75" style="47" customWidth="1"/>
     <col min="2" max="2" width="26.5" customWidth="1"/>
     <col min="3" max="50" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="47" customFormat="1" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" s="47" customFormat="1" ht="98" x14ac:dyDescent="0.3">
       <c r="B1" s="47" t="s">
         <v>337</v>
       </c>
@@ -11301,227 +11301,227 @@
         <v>381</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A2" s="47" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A3" s="47" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A4" s="47" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A5" s="47" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A7" s="47" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A9" s="47" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="47" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="47" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="47" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" ht="28" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="47" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
         <v>381</v>
       </c>
@@ -11534,18 +11534,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I1018"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="2" width="28.625" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="16.125" customWidth="1"/>
-    <col min="5" max="8" width="7.625" customWidth="1"/>
-    <col min="9" max="9" width="50.125" customWidth="1"/>
-    <col min="10" max="26" width="7.625" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.08203125" customWidth="1"/>
+    <col min="5" max="8" width="7.58203125" customWidth="1"/>
+    <col min="9" max="9" width="50.08203125" customWidth="1"/>
+    <col min="10" max="26" width="7.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -11565,12 +11565,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -11598,22 +11598,22 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
@@ -11621,1079 +11621,1079 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1016" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1017" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1018" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1016" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1017" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1018" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -12706,13 +12706,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.125" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1"/>
+    <col min="5" max="5" width="20.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>134</v>
       </c>
@@ -12729,36 +12729,36 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
         <v>139</v>
       </c>
@@ -12766,32 +12766,32 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
         <v>146</v>
       </c>
@@ -12805,14 +12805,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E3900F-A3B7-49CE-A2A1-7EDF5100099A}">
   <dimension ref="B3:H25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.875" customWidth="1"/>
-    <col min="3" max="3" width="54.125" customWidth="1"/>
-    <col min="4" max="4" width="35.125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="54.08203125" customWidth="1"/>
+    <col min="4" max="4" width="35.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D3" s="6" t="s">
         <v>158</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>3</v>
       </c>
@@ -12868,97 +12868,97 @@
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>22</v>
       </c>
